--- a/Versão5/GIS/Ontologia_Kml_2x2.xlsx
+++ b/Versão5/GIS/Ontologia_Kml_2x2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\BIM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\GIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2BC3C16-3035-46EF-ADE1-B754261AC1FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC37ADF8-9E6D-458B-B428-7DBB5CF02FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="681" activeTab="1" xr2:uid="{EADD6BF3-7ABC-4ACF-B5B1-0F5DE0265229}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="681" activeTab="1" xr2:uid="{EADD6BF3-7ABC-4ACF-B5B1-0F5DE0265229}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="16" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1842" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1926" uniqueCount="356">
   <si>
     <t>Organização</t>
   </si>
@@ -426,9 +426,6 @@
     <t>Elemento de feição geográfica em KML. Define o elemento mais comum que representa uma feição geográfica individual e pode associar um nome, descrição, estilo e uma geometria.</t>
   </si>
   <si>
-    <t>Elemento KML</t>
-  </si>
-  <si>
     <t>&lt;Document&gt;</t>
   </si>
   <si>
@@ -1086,16 +1083,67 @@
     <t>Macros</t>
   </si>
   <si>
-    <t>API.Revit</t>
-  </si>
-  <si>
-    <t>Aplicação Revit</t>
-  </si>
-  <si>
-    <t>Aplicativo Revit</t>
-  </si>
-  <si>
-    <t>Revit Aplication</t>
+    <t>Função.Auxiliar</t>
+  </si>
+  <si>
+    <t>Define uma Função Auxiliar (helper) numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol de ayudante en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Helper Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Global</t>
+  </si>
+  <si>
+    <t>Define uma Função Global numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol global en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Global Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Local</t>
+  </si>
+  <si>
+    <t>Define uma Função Local numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol local en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Local Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Filtro</t>
+  </si>
+  <si>
+    <t>Define uma Função para filtrar objetos numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina una función para filtrar objetos en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Function to filter objects in an application</t>
+  </si>
+  <si>
+    <t>Códigos.Visuais</t>
+  </si>
+  <si>
+    <t>Bloco.de.Código</t>
+  </si>
+  <si>
+    <t>Define um Código escrito em sistemas de programação visual</t>
+  </si>
+  <si>
+    <t>Define un código escrito en sistemas de programación visual</t>
+  </si>
+  <si>
+    <t>Defines a Code written in visual programming systems</t>
   </si>
 </sst>
 </file>
@@ -1433,7 +1481,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1608,9 +1656,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1619,6 +1664,12 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1908,11 +1959,13 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
+        <color rgb="FF9C0006"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2308,14 +2361,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{643CFCF6-0637-46A8-9CC0-1BF6FB3A6D15}">
   <sheetPr codeName="Planilha14"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultRowHeight="7" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.453125" customWidth="1"/>
-    <col min="2" max="2" width="65.36328125" style="29" customWidth="1"/>
-    <col min="3" max="3" width="4.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5" customWidth="1"/>
+    <col min="2" max="2" width="65.33203125" style="29" customWidth="1"/>
+    <col min="3" max="3" width="4.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -2326,7 +2379,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
@@ -2337,18 +2390,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>13</v>
       </c>
@@ -2359,7 +2412,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>15</v>
       </c>
@@ -2371,7 +2424,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>16</v>
       </c>
@@ -2383,7 +2436,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>17</v>
       </c>
@@ -2394,7 +2447,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>19</v>
       </c>
@@ -2405,7 +2458,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>0</v>
       </c>
@@ -2416,7 +2469,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>22</v>
       </c>
@@ -2427,7 +2480,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>24</v>
       </c>
@@ -2438,7 +2491,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>25</v>
       </c>
@@ -2449,7 +2502,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>26</v>
       </c>
@@ -2460,7 +2513,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>27</v>
       </c>
@@ -2471,7 +2524,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>28</v>
       </c>
@@ -2482,41 +2535,41 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>90</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B18" s="7">
         <f ca="1">NOW()</f>
-        <v>46264.564807060182</v>
+        <v>46268.698208912036</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>31</v>
       </c>
@@ -2527,7 +2580,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>33</v>
       </c>
@@ -2538,7 +2591,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>34</v>
       </c>
@@ -2549,18 +2602,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>36</v>
       </c>
@@ -2572,7 +2625,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>38</v>
       </c>
@@ -2594,36 +2647,36 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B21B10B-C8BF-4318-B9A8-B9240E89A4C8}">
-  <dimension ref="A1:AD63"/>
-  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AD67"/>
+  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" customWidth="1"/>
-    <col min="3" max="3" width="10.6328125" customWidth="1"/>
-    <col min="4" max="4" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.5" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" customWidth="1"/>
+    <col min="4" max="4" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5" customWidth="1"/>
-    <col min="6" max="6" width="19.453125" customWidth="1"/>
-    <col min="7" max="11" width="7.81640625" customWidth="1"/>
-    <col min="12" max="12" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="8.6328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="23.36328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="155.453125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="144.81640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="134.6328125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.6328125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.1796875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="23.36328125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.5" customWidth="1"/>
+    <col min="7" max="11" width="7.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="155.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="144.83203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="134.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="25" max="26" width="9" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:30" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="58">
         <v>1</v>
       </c>
@@ -2712,10 +2765,10 @@
         <v>62</v>
       </c>
       <c r="AD1" s="9" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="2" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="31">
         <v>2</v>
       </c>
@@ -2732,7 +2785,7 @@
         <v>96</v>
       </c>
       <c r="F2" s="36" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G2" s="32" t="s">
         <v>2</v>
@@ -2766,7 +2819,7 @@
         <v>Kml.Arquivo</v>
       </c>
       <c r="P2" s="37" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Q2" s="14" t="str">
         <f>_xlfn.TRANSLATE(P2,"pt","es")</f>
@@ -2814,10 +2867,10 @@
         <v>2</v>
       </c>
       <c r="AD2" s="37" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="3" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="31">
         <v>3</v>
       </c>
@@ -2834,7 +2887,7 @@
         <v>96</v>
       </c>
       <c r="F3" s="36" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G3" s="32" t="s">
         <v>2</v>
@@ -2868,10 +2921,10 @@
         <v>Kml.Atributo</v>
       </c>
       <c r="P3" s="37" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q3" s="14" t="s">
         <v>141</v>
-      </c>
-      <c r="Q3" s="14" t="s">
-        <v>142</v>
       </c>
       <c r="R3" s="14" t="str">
         <f t="shared" si="4"/>
@@ -2915,10 +2968,10 @@
         <v>2</v>
       </c>
       <c r="AD3" s="37" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="4" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="31">
         <v>4</v>
       </c>
@@ -2935,7 +2988,7 @@
         <v>96</v>
       </c>
       <c r="F4" s="36" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G4" s="32" t="s">
         <v>2</v>
@@ -2969,7 +3022,7 @@
         <v>Kml.Box</v>
       </c>
       <c r="P4" s="37" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q4" s="14" t="str">
         <f t="shared" ref="Q4:Q19" si="9">_xlfn.TRANSLATE(P4,"pt","es")</f>
@@ -3017,10 +3070,10 @@
         <v>2</v>
       </c>
       <c r="AD4" s="37" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="5" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="31">
         <v>5</v>
       </c>
@@ -3037,7 +3090,7 @@
         <v>96</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G5" s="32" t="s">
         <v>2</v>
@@ -3071,7 +3124,7 @@
         <v>Kml.Box.Cardinal.Leste</v>
       </c>
       <c r="P5" s="37" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q5" s="14" t="str">
         <f t="shared" si="9"/>
@@ -3119,10 +3172,10 @@
         <v>2</v>
       </c>
       <c r="AD5" s="37" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="31">
         <v>6</v>
       </c>
@@ -3139,7 +3192,7 @@
         <v>96</v>
       </c>
       <c r="F6" s="36" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G6" s="32" t="s">
         <v>2</v>
@@ -3173,7 +3226,7 @@
         <v>Kml.Box.Cardinal.Norte</v>
       </c>
       <c r="P6" s="37" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q6" s="14" t="str">
         <f t="shared" si="9"/>
@@ -3221,10 +3274,10 @@
         <v>2</v>
       </c>
       <c r="AD6" s="37" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="7" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="31">
         <v>7</v>
       </c>
@@ -3241,7 +3294,7 @@
         <v>96</v>
       </c>
       <c r="F7" s="36" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G7" s="32" t="s">
         <v>2</v>
@@ -3275,7 +3328,7 @@
         <v>Kml.Box.Cardinal.Oeste</v>
       </c>
       <c r="P7" s="37" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q7" s="14" t="str">
         <f t="shared" si="9"/>
@@ -3323,10 +3376,10 @@
         <v>2</v>
       </c>
       <c r="AD7" s="37" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="31">
         <v>8</v>
       </c>
@@ -3343,7 +3396,7 @@
         <v>96</v>
       </c>
       <c r="F8" s="36" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G8" s="32" t="s">
         <v>2</v>
@@ -3377,7 +3430,7 @@
         <v>Kml.Box.Cardinal.Sul</v>
       </c>
       <c r="P8" s="37" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q8" s="14" t="str">
         <f t="shared" si="9"/>
@@ -3425,10 +3478,10 @@
         <v>2</v>
       </c>
       <c r="AD8" s="37" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="31">
         <v>9</v>
       </c>
@@ -3445,7 +3498,7 @@
         <v>96</v>
       </c>
       <c r="F9" s="36" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G9" s="32" t="s">
         <v>2</v>
@@ -3479,7 +3532,7 @@
         <v>Kml.Box.Rotado</v>
       </c>
       <c r="P9" s="37" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q9" s="14" t="str">
         <f t="shared" si="9"/>
@@ -3527,10 +3580,10 @@
         <v>2</v>
       </c>
       <c r="AD9" s="37" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="10" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="31">
         <v>10</v>
       </c>
@@ -3547,7 +3600,7 @@
         <v>96</v>
       </c>
       <c r="F10" s="36" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G10" s="32" t="s">
         <v>2</v>
@@ -3629,10 +3682,10 @@
         <v>2</v>
       </c>
       <c r="AD10" s="37" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="31">
         <v>11</v>
       </c>
@@ -3649,7 +3702,7 @@
         <v>96</v>
       </c>
       <c r="F11" s="36" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G11" s="32" t="s">
         <v>2</v>
@@ -3683,7 +3736,7 @@
         <v>Kml.Camara.Alcance</v>
       </c>
       <c r="P11" s="37" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Q11" s="14" t="str">
         <f t="shared" si="9"/>
@@ -3731,10 +3784,10 @@
         <v>2</v>
       </c>
       <c r="AD11" s="37" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="12" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="31">
         <v>12</v>
       </c>
@@ -3751,7 +3804,7 @@
         <v>96</v>
       </c>
       <c r="F12" s="36" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G12" s="32" t="s">
         <v>2</v>
@@ -3833,10 +3886,10 @@
         <v>2</v>
       </c>
       <c r="AD12" s="37" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="13" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="31">
         <v>13</v>
       </c>
@@ -3853,7 +3906,7 @@
         <v>96</v>
       </c>
       <c r="F13" s="36" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G13" s="32" t="s">
         <v>2</v>
@@ -3887,7 +3940,7 @@
         <v>Kml.Camara.Azimut</v>
       </c>
       <c r="P13" s="37" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q13" s="14" t="str">
         <f t="shared" si="9"/>
@@ -3935,10 +3988,10 @@
         <v>2</v>
       </c>
       <c r="AD13" s="37" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="14" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="31">
         <v>14</v>
       </c>
@@ -3955,7 +4008,7 @@
         <v>96</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G14" s="32" t="s">
         <v>2</v>
@@ -3989,7 +4042,7 @@
         <v>Kml.Dado.Estendido</v>
       </c>
       <c r="P14" s="37" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q14" s="14" t="str">
         <f t="shared" si="9"/>
@@ -4037,10 +4090,10 @@
         <v>2</v>
       </c>
       <c r="AD14" s="37" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="15" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="31">
         <v>15</v>
       </c>
@@ -4057,7 +4110,7 @@
         <v>96</v>
       </c>
       <c r="F15" s="36" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G15" s="32" t="s">
         <v>2</v>
@@ -4091,7 +4144,7 @@
         <v>Kml.Dado.Estendido.Dado</v>
       </c>
       <c r="P15" s="37" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q15" s="14" t="str">
         <f t="shared" si="9"/>
@@ -4139,10 +4192,10 @@
         <v>2</v>
       </c>
       <c r="AD15" s="37" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="16" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="31">
         <v>16</v>
       </c>
@@ -4159,7 +4212,7 @@
         <v>96</v>
       </c>
       <c r="F16" s="36" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G16" s="32" t="s">
         <v>2</v>
@@ -4193,7 +4246,7 @@
         <v>Kml.Dado.Estendido.Dado.Simples</v>
       </c>
       <c r="P16" s="37" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q16" s="14" t="str">
         <f t="shared" si="9"/>
@@ -4241,10 +4294,10 @@
         <v>2</v>
       </c>
       <c r="AD16" s="37" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="17" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="31">
         <v>17</v>
       </c>
@@ -4261,7 +4314,7 @@
         <v>96</v>
       </c>
       <c r="F17" s="36" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G17" s="32" t="s">
         <v>2</v>
@@ -4295,7 +4348,7 @@
         <v>Kml.Dado.Estendido.Esquema</v>
       </c>
       <c r="P17" s="37" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Q17" s="14" t="str">
         <f t="shared" si="9"/>
@@ -4343,10 +4396,10 @@
         <v>2</v>
       </c>
       <c r="AD17" s="37" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="18" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="31">
         <v>18</v>
       </c>
@@ -4363,7 +4416,7 @@
         <v>96</v>
       </c>
       <c r="F18" s="36" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G18" s="32" t="s">
         <v>2</v>
@@ -4397,7 +4450,7 @@
         <v>Kml.Dado.Estendido.Esquema.Dado</v>
       </c>
       <c r="P18" s="37" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q18" s="14" t="str">
         <f t="shared" si="9"/>
@@ -4445,10 +4498,10 @@
         <v>2</v>
       </c>
       <c r="AD18" s="37" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="19" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="31">
         <v>19</v>
       </c>
@@ -4465,7 +4518,7 @@
         <v>96</v>
       </c>
       <c r="F19" s="36" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G19" s="32" t="s">
         <v>2</v>
@@ -4499,7 +4552,7 @@
         <v>Kml.Documento</v>
       </c>
       <c r="P19" s="37" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q19" s="14" t="str">
         <f t="shared" si="9"/>
@@ -4547,10 +4600,10 @@
         <v>2</v>
       </c>
       <c r="AD19" s="37" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="20" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="31">
         <v>20</v>
       </c>
@@ -4567,7 +4620,7 @@
         <v>96</v>
       </c>
       <c r="F20" s="36" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G20" s="32" t="s">
         <v>2</v>
@@ -4601,10 +4654,10 @@
         <v>Kml.Elemento.N0</v>
       </c>
       <c r="P20" s="37" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Q20" s="37" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="R20" s="14" t="str">
         <f t="shared" si="4"/>
@@ -4648,10 +4701,10 @@
         <v>2</v>
       </c>
       <c r="AD20" s="37" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="21" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="31">
         <v>21</v>
       </c>
@@ -4668,7 +4721,7 @@
         <v>96</v>
       </c>
       <c r="F21" s="36" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G21" s="32" t="s">
         <v>2</v>
@@ -4702,10 +4755,10 @@
         <v>Kml.Elemento.N1</v>
       </c>
       <c r="P21" s="37" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q21" s="37" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="R21" s="14" t="str">
         <f t="shared" si="4"/>
@@ -4749,10 +4802,10 @@
         <v>2</v>
       </c>
       <c r="AD21" s="37" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="22" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="31">
         <v>22</v>
       </c>
@@ -4769,7 +4822,7 @@
         <v>96</v>
       </c>
       <c r="F22" s="36" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G22" s="32" t="s">
         <v>2</v>
@@ -4803,10 +4856,10 @@
         <v>Kml.Elemento.N2</v>
       </c>
       <c r="P22" s="37" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q22" s="37" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R22" s="14" t="str">
         <f t="shared" si="4"/>
@@ -4850,10 +4903,10 @@
         <v>2</v>
       </c>
       <c r="AD22" s="37" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="23" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="31">
         <v>23</v>
       </c>
@@ -4870,7 +4923,7 @@
         <v>96</v>
       </c>
       <c r="F23" s="36" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G23" s="32" t="s">
         <v>2</v>
@@ -4904,10 +4957,10 @@
         <v>Kml.Elemento.N3</v>
       </c>
       <c r="P23" s="37" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q23" s="37" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R23" s="14" t="str">
         <f t="shared" si="4"/>
@@ -4951,10 +5004,10 @@
         <v>2</v>
       </c>
       <c r="AD23" s="37" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="24" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="31">
         <v>24</v>
       </c>
@@ -4971,7 +5024,7 @@
         <v>96</v>
       </c>
       <c r="F24" s="36" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G24" s="32" t="s">
         <v>2</v>
@@ -5005,10 +5058,10 @@
         <v>Kml.Elemento.N4</v>
       </c>
       <c r="P24" s="37" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Q24" s="37" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R24" s="14" t="str">
         <f t="shared" si="4"/>
@@ -5052,10 +5105,10 @@
         <v>2</v>
       </c>
       <c r="AD24" s="37" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="25" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="31">
         <v>25</v>
       </c>
@@ -5072,7 +5125,7 @@
         <v>96</v>
       </c>
       <c r="F25" s="36" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G25" s="32" t="s">
         <v>2</v>
@@ -5106,10 +5159,10 @@
         <v>Kml.Elemento.N5</v>
       </c>
       <c r="P25" s="37" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q25" s="37" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R25" s="14" t="str">
         <f t="shared" si="4"/>
@@ -5153,10 +5206,10 @@
         <v>2</v>
       </c>
       <c r="AD25" s="37" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="26" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="31">
         <v>26</v>
       </c>
@@ -5173,7 +5226,7 @@
         <v>96</v>
       </c>
       <c r="F26" s="36" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G26" s="32" t="s">
         <v>2</v>
@@ -5255,10 +5308,10 @@
         <v>2</v>
       </c>
       <c r="AD26" s="37" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="27" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="31">
         <v>27</v>
       </c>
@@ -5275,7 +5328,7 @@
         <v>96</v>
       </c>
       <c r="F27" s="36" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G27" s="32" t="s">
         <v>2</v>
@@ -5357,10 +5410,10 @@
         <v>2</v>
       </c>
       <c r="AD27" s="37" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="28" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="31">
         <v>28</v>
       </c>
@@ -5377,7 +5430,7 @@
         <v>96</v>
       </c>
       <c r="F28" s="36" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G28" s="32" t="s">
         <v>2</v>
@@ -5411,7 +5464,7 @@
         <v>Kml.Estilo.Cor</v>
       </c>
       <c r="P28" s="37" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q28" s="14" t="str">
         <f t="shared" si="10"/>
@@ -5459,10 +5512,10 @@
         <v>2</v>
       </c>
       <c r="AD28" s="37" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="29" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="31">
         <v>29</v>
       </c>
@@ -5479,7 +5532,7 @@
         <v>96</v>
       </c>
       <c r="F29" s="36" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G29" s="32" t="s">
         <v>2</v>
@@ -5513,7 +5566,7 @@
         <v>Kml.Estilo.Espessura</v>
       </c>
       <c r="P29" s="37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q29" s="14" t="str">
         <f t="shared" si="10"/>
@@ -5561,10 +5614,10 @@
         <v>2</v>
       </c>
       <c r="AD29" s="37" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="30" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="31">
         <v>30</v>
       </c>
@@ -5581,7 +5634,7 @@
         <v>96</v>
       </c>
       <c r="F30" s="36" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G30" s="32" t="s">
         <v>2</v>
@@ -5663,10 +5716,10 @@
         <v>2</v>
       </c>
       <c r="AD30" s="37" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="31" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="31">
         <v>31</v>
       </c>
@@ -5683,7 +5736,7 @@
         <v>96</v>
       </c>
       <c r="F31" s="36" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G31" s="32" t="s">
         <v>2</v>
@@ -5765,10 +5818,10 @@
         <v>2</v>
       </c>
       <c r="AD31" s="37" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="32" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="31">
         <v>32</v>
       </c>
@@ -5785,7 +5838,7 @@
         <v>96</v>
       </c>
       <c r="F32" s="36" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G32" s="32" t="s">
         <v>2</v>
@@ -5867,10 +5920,10 @@
         <v>2</v>
       </c>
       <c r="AD32" s="37" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="33" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="33" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="31">
         <v>33</v>
       </c>
@@ -5887,7 +5940,7 @@
         <v>96</v>
       </c>
       <c r="F33" s="36" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G33" s="32" t="s">
         <v>2</v>
@@ -5921,7 +5974,7 @@
         <v>Kml.Estilo.Usado</v>
       </c>
       <c r="P33" s="37" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q33" s="14" t="str">
         <f t="shared" si="10"/>
@@ -5969,10 +6022,10 @@
         <v>2</v>
       </c>
       <c r="AD33" s="37" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="34" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="34" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="31">
         <v>34</v>
       </c>
@@ -5989,7 +6042,7 @@
         <v>96</v>
       </c>
       <c r="F34" s="36" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G34" s="32" t="s">
         <v>2</v>
@@ -6023,7 +6076,7 @@
         <v>Kml.Estilo.Visibilidade</v>
       </c>
       <c r="P34" s="37" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q34" s="14" t="str">
         <f t="shared" si="10"/>
@@ -6052,7 +6105,7 @@
         <v>64</v>
       </c>
       <c r="X34" s="30" t="str">
-        <f t="shared" ref="X34:X63" si="19">CONCATENATE("Key-Kml-",A34)</f>
+        <f t="shared" ref="X34:X67" si="19">CONCATENATE("Key-Kml-",A34)</f>
         <v>Key-Kml-34</v>
       </c>
       <c r="Y34" s="14" t="s">
@@ -6071,10 +6124,10 @@
         <v>2</v>
       </c>
       <c r="AD34" s="37" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="35" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="35" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="31">
         <v>35</v>
       </c>
@@ -6091,7 +6144,7 @@
         <v>96</v>
       </c>
       <c r="F35" s="36" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G35" s="32" t="s">
         <v>2</v>
@@ -6125,7 +6178,7 @@
         <v>Kml.Extrusão</v>
       </c>
       <c r="P35" s="37" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Q35" s="14" t="str">
         <f t="shared" si="10"/>
@@ -6173,10 +6226,10 @@
         <v>2</v>
       </c>
       <c r="AD35" s="37" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="36" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="36" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="31">
         <v>36</v>
       </c>
@@ -6193,7 +6246,7 @@
         <v>96</v>
       </c>
       <c r="F36" s="36" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G36" s="32" t="s">
         <v>2</v>
@@ -6227,7 +6280,7 @@
         <v>Kml.Gira.X</v>
       </c>
       <c r="P36" s="37" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q36" s="14" t="str">
         <f t="shared" si="10"/>
@@ -6275,10 +6328,10 @@
         <v>2</v>
       </c>
       <c r="AD36" s="37" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="37" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="37" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="31">
         <v>37</v>
       </c>
@@ -6295,7 +6348,7 @@
         <v>96</v>
       </c>
       <c r="F37" s="36" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G37" s="32" t="s">
         <v>2</v>
@@ -6329,7 +6382,7 @@
         <v>Kml.Gira.Z</v>
       </c>
       <c r="P37" s="37" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q37" s="14" t="str">
         <f t="shared" si="10"/>
@@ -6377,10 +6430,10 @@
         <v>2</v>
       </c>
       <c r="AD37" s="37" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="38" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="38" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="31">
         <v>38</v>
       </c>
@@ -6397,7 +6450,7 @@
         <v>96</v>
       </c>
       <c r="F38" s="36" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G38" s="32" t="s">
         <v>2</v>
@@ -6479,10 +6532,10 @@
         <v>2</v>
       </c>
       <c r="AD38" s="37" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="39" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="39" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="31">
         <v>39</v>
       </c>
@@ -6499,7 +6552,7 @@
         <v>96</v>
       </c>
       <c r="F39" s="36" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G39" s="32" t="s">
         <v>2</v>
@@ -6581,10 +6634,10 @@
         <v>2</v>
       </c>
       <c r="AD39" s="37" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="40" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="40" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="31">
         <v>41</v>
       </c>
@@ -6601,7 +6654,7 @@
         <v>96</v>
       </c>
       <c r="F40" s="36" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G40" s="32" t="s">
         <v>2</v>
@@ -6683,10 +6736,10 @@
         <v>2</v>
       </c>
       <c r="AD40" s="37" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="41" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="41" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="31">
         <v>42</v>
       </c>
@@ -6703,7 +6756,7 @@
         <v>96</v>
       </c>
       <c r="F41" s="36" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G41" s="32" t="s">
         <v>2</v>
@@ -6737,7 +6790,7 @@
         <v>Kml.Lugar.Ponto.Altitude</v>
       </c>
       <c r="P41" s="37" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q41" s="14" t="str">
         <f t="shared" si="10"/>
@@ -6785,10 +6838,10 @@
         <v>2</v>
       </c>
       <c r="AD41" s="37" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="42" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="42" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="31">
         <v>43</v>
       </c>
@@ -6805,7 +6858,7 @@
         <v>96</v>
       </c>
       <c r="F42" s="36" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G42" s="32" t="s">
         <v>2</v>
@@ -6839,7 +6892,7 @@
         <v>Kml.Lugar.Ponto.AltitudeModo</v>
       </c>
       <c r="P42" s="37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q42" s="14" t="str">
         <f t="shared" si="10"/>
@@ -6887,10 +6940,10 @@
         <v>2</v>
       </c>
       <c r="AD42" s="37" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="43" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="43" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="31">
         <v>44</v>
       </c>
@@ -6907,7 +6960,7 @@
         <v>96</v>
       </c>
       <c r="F43" s="36" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G43" s="32" t="s">
         <v>2</v>
@@ -6941,7 +6994,7 @@
         <v>Kml.Lugar.Ponto.Latitude</v>
       </c>
       <c r="P43" s="37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q43" s="14" t="str">
         <f t="shared" si="10"/>
@@ -6989,10 +7042,10 @@
         <v>2</v>
       </c>
       <c r="AD43" s="37" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="44" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="44" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="31">
         <v>45</v>
       </c>
@@ -7009,7 +7062,7 @@
         <v>96</v>
       </c>
       <c r="F44" s="36" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G44" s="32" t="s">
         <v>2</v>
@@ -7043,7 +7096,7 @@
         <v>Kml.Lugar.Ponto.Longitude</v>
       </c>
       <c r="P44" s="37" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q44" s="14" t="str">
         <f t="shared" si="10"/>
@@ -7091,10 +7144,10 @@
         <v>2</v>
       </c>
       <c r="AD44" s="37" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="45" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="45" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="31">
         <v>46</v>
       </c>
@@ -7111,7 +7164,7 @@
         <v>96</v>
       </c>
       <c r="F45" s="36" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G45" s="32" t="s">
         <v>2</v>
@@ -7145,7 +7198,7 @@
         <v>Kml.Lugar.Ponto.XYZ</v>
       </c>
       <c r="P45" s="37" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q45" s="14" t="str">
         <f t="shared" si="10"/>
@@ -7193,10 +7246,10 @@
         <v>2</v>
       </c>
       <c r="AD45" s="37" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="46" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="46" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="31">
         <v>47</v>
       </c>
@@ -7213,7 +7266,7 @@
         <v>96</v>
       </c>
       <c r="F46" s="36" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G46" s="32" t="s">
         <v>2</v>
@@ -7295,10 +7348,10 @@
         <v>2</v>
       </c>
       <c r="AD46" s="37" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="47" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="47" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="31">
         <v>48</v>
       </c>
@@ -7315,7 +7368,7 @@
         <v>96</v>
       </c>
       <c r="F47" s="36" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G47" s="32" t="s">
         <v>2</v>
@@ -7397,10 +7450,10 @@
         <v>2</v>
       </c>
       <c r="AD47" s="37" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="48" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="48" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="31">
         <v>49</v>
       </c>
@@ -7417,7 +7470,7 @@
         <v>96</v>
       </c>
       <c r="F48" s="36" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G48" s="32" t="s">
         <v>2</v>
@@ -7499,10 +7552,10 @@
         <v>2</v>
       </c>
       <c r="AD48" s="37" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="49" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="49" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="31">
         <v>40</v>
       </c>
@@ -7519,7 +7572,7 @@
         <v>96</v>
       </c>
       <c r="F49" s="36" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G49" s="32" t="s">
         <v>2</v>
@@ -7553,7 +7606,7 @@
         <v>Kml.Lugar.Segmento.Projeção</v>
       </c>
       <c r="P49" s="37" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="Q49" s="14" t="str">
         <f t="shared" si="10"/>
@@ -7601,10 +7654,10 @@
         <v>2</v>
       </c>
       <c r="AD49" s="37" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="50" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="50" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="31">
         <v>50</v>
       </c>
@@ -7621,7 +7674,7 @@
         <v>96</v>
       </c>
       <c r="F50" s="36" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G50" s="32" t="s">
         <v>2</v>
@@ -7703,10 +7756,10 @@
         <v>2</v>
       </c>
       <c r="AD50" s="37" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="51" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="51" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="31">
         <v>51</v>
       </c>
@@ -7723,7 +7776,7 @@
         <v>96</v>
       </c>
       <c r="F51" s="36" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G51" s="32" t="s">
         <v>2</v>
@@ -7757,7 +7810,7 @@
         <v>Kml.Nome</v>
       </c>
       <c r="P51" s="37" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q51" s="14" t="str">
         <f t="shared" si="10"/>
@@ -7805,10 +7858,10 @@
         <v>2</v>
       </c>
       <c r="AD51" s="37" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="52" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="52" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="31">
         <v>52</v>
       </c>
@@ -7825,7 +7878,7 @@
         <v>96</v>
       </c>
       <c r="F52" s="36" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G52" s="32" t="s">
         <v>2</v>
@@ -7859,7 +7912,7 @@
         <v>Kml.Pasta</v>
       </c>
       <c r="P52" s="37" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q52" s="14" t="str">
         <f t="shared" si="10"/>
@@ -7907,10 +7960,10 @@
         <v>2</v>
       </c>
       <c r="AD52" s="37" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="53" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="53" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="31">
         <v>53</v>
       </c>
@@ -7927,7 +7980,7 @@
         <v>96</v>
       </c>
       <c r="F53" s="36" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G53" s="32" t="s">
         <v>2</v>
@@ -7961,7 +8014,7 @@
         <v>Kml.Pasta.Aberta</v>
       </c>
       <c r="P53" s="37" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="Q53" s="14" t="str">
         <f t="shared" si="10"/>
@@ -8009,10 +8062,10 @@
         <v>2</v>
       </c>
       <c r="AD53" s="37" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="54" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="54" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="31">
         <v>54</v>
       </c>
@@ -8029,7 +8082,7 @@
         <v>96</v>
       </c>
       <c r="F54" s="36" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G54" s="32" t="s">
         <v>2</v>
@@ -8063,7 +8116,7 @@
         <v>Kml.Region</v>
       </c>
       <c r="P54" s="37" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q54" s="14" t="str">
         <f t="shared" si="10"/>
@@ -8111,10 +8164,10 @@
         <v>2</v>
       </c>
       <c r="AD54" s="37" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="55" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="55" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="31">
         <v>55</v>
       </c>
@@ -8131,7 +8184,7 @@
         <v>96</v>
       </c>
       <c r="F55" s="36" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G55" s="32" t="s">
         <v>2</v>
@@ -8213,10 +8266,10 @@
         <v>2</v>
       </c>
       <c r="AD55" s="37" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="56" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="56" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="31">
         <v>56</v>
       </c>
@@ -8233,7 +8286,7 @@
         <v>96</v>
       </c>
       <c r="F56" s="36" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G56" s="32" t="s">
         <v>2</v>
@@ -8315,10 +8368,10 @@
         <v>2</v>
       </c>
       <c r="AD56" s="37" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="57" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="57" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="31">
         <v>57</v>
       </c>
@@ -8335,7 +8388,7 @@
         <v>96</v>
       </c>
       <c r="F57" s="36" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G57" s="32" t="s">
         <v>2</v>
@@ -8417,10 +8470,10 @@
         <v>2</v>
       </c>
       <c r="AD57" s="37" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="58" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="58" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="31">
         <v>58</v>
       </c>
@@ -8437,7 +8490,7 @@
         <v>96</v>
       </c>
       <c r="F58" s="36" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G58" s="32" t="s">
         <v>2</v>
@@ -8519,10 +8572,10 @@
         <v>2</v>
       </c>
       <c r="AD58" s="37" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="59" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="59" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="31">
         <v>59</v>
       </c>
@@ -8539,7 +8592,7 @@
         <v>96</v>
       </c>
       <c r="F59" s="36" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G59" s="32" t="s">
         <v>2</v>
@@ -8573,7 +8626,7 @@
         <v>Kml.Tempo.Momento</v>
       </c>
       <c r="P59" s="37" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q59" s="14" t="str">
         <f t="shared" si="10"/>
@@ -8621,10 +8674,10 @@
         <v>2</v>
       </c>
       <c r="AD59" s="37" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="60" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="60" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="31">
         <v>60</v>
       </c>
@@ -8641,7 +8694,7 @@
         <v>96</v>
       </c>
       <c r="F60" s="36" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G60" s="32" t="s">
         <v>2</v>
@@ -8675,7 +8728,7 @@
         <v>Kml.Tempo.Momento.Final</v>
       </c>
       <c r="P60" s="37" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q60" s="14" t="str">
         <f t="shared" si="10"/>
@@ -8723,10 +8776,10 @@
         <v>2</v>
       </c>
       <c r="AD60" s="37" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="61" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="61" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="31">
         <v>61</v>
       </c>
@@ -8743,7 +8796,7 @@
         <v>96</v>
       </c>
       <c r="F61" s="36" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G61" s="32" t="s">
         <v>2</v>
@@ -8777,7 +8830,7 @@
         <v>Kml.Tempo.Momento.Inicial</v>
       </c>
       <c r="P61" s="37" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Q61" s="14" t="str">
         <f t="shared" si="10"/>
@@ -8825,10 +8878,10 @@
         <v>2</v>
       </c>
       <c r="AD61" s="37" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="62" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="62" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="31">
         <v>62</v>
       </c>
@@ -8845,7 +8898,7 @@
         <v>96</v>
       </c>
       <c r="F62" s="36" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G62" s="32" t="s">
         <v>2</v>
@@ -8927,28 +8980,28 @@
         <v>2</v>
       </c>
       <c r="AD62" s="37" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="63" spans="1:30" s="63" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="63" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="31">
         <v>63</v>
       </c>
-      <c r="B63" s="11" t="s">
+      <c r="B63" s="63" t="s">
+        <v>331</v>
+      </c>
+      <c r="C63" s="64" t="s">
         <v>332</v>
       </c>
-      <c r="C63" s="60" t="s">
+      <c r="D63" s="64" t="s">
+        <v>334</v>
+      </c>
+      <c r="E63" s="64" t="s">
         <v>333</v>
       </c>
-      <c r="D63" s="60" t="s">
+      <c r="F63" s="64" t="s">
         <v>335</v>
       </c>
-      <c r="E63" s="60" t="s">
-        <v>334</v>
-      </c>
-      <c r="F63" s="60" t="s">
-        <v>336</v>
-      </c>
       <c r="G63" s="32" t="s">
         <v>2</v>
       </c>
@@ -8965,7 +9018,7 @@
         <v>2</v>
       </c>
       <c r="L63" s="13" t="str">
-        <f t="shared" ref="L63:O63" si="20">SUBSTITUTE(CONCATENATE("", C63), ".", " ")</f>
+        <f t="shared" ref="L63:O67" si="20">SUBSTITUTE(CONCATENATE("", C63), ".", " ")</f>
         <v>De API</v>
       </c>
       <c r="M63" s="13" t="str">
@@ -8978,29 +9031,29 @@
       </c>
       <c r="O63" s="13" t="str">
         <f t="shared" si="20"/>
-        <v>API Revit</v>
+        <v>Função Auxiliar</v>
       </c>
       <c r="P63" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q63" s="14" t="s">
         <v>337</v>
       </c>
-      <c r="Q63" s="14" t="s">
+      <c r="R63" s="14" t="s">
         <v>338</v>
       </c>
-      <c r="R63" s="14" t="s">
-        <v>339</v>
-      </c>
       <c r="S63" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T63" s="14" t="str">
-        <f t="shared" ref="T63:V63" si="21">SUBSTITUTE(C63, ".", " ")</f>
+        <f t="shared" ref="T63:V67" si="21">SUBSTITUTE(C63, ".", " ")</f>
         <v>De API</v>
       </c>
       <c r="U63" s="14" t="str">
         <f t="shared" si="21"/>
         <v>Macros</v>
       </c>
-      <c r="V63" s="61" t="str">
+      <c r="V63" s="60" t="str">
         <f t="shared" si="21"/>
         <v>Métodos</v>
       </c>
@@ -9011,22 +9064,422 @@
         <f t="shared" si="19"/>
         <v>Key-Kml-63</v>
       </c>
-      <c r="Y63" s="62" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z63" s="62" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA63" s="62" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB63" s="62" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC63" s="62" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD63" s="62" t="s">
+      <c r="Y63" s="61" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z63" s="61" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA63" s="61" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB63" s="61" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC63" s="61" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD63" s="61" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="31">
+        <v>64</v>
+      </c>
+      <c r="B64" s="63" t="s">
+        <v>331</v>
+      </c>
+      <c r="C64" s="64" t="s">
+        <v>332</v>
+      </c>
+      <c r="D64" s="64" t="s">
+        <v>334</v>
+      </c>
+      <c r="E64" s="64" t="s">
+        <v>333</v>
+      </c>
+      <c r="F64" s="64" t="s">
+        <v>339</v>
+      </c>
+      <c r="G64" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="H64" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="I64" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="J64" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="K64" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="L64" s="13" t="str">
+        <f t="shared" si="20"/>
+        <v>De API</v>
+      </c>
+      <c r="M64" s="13" t="str">
+        <f t="shared" si="20"/>
+        <v>Macros</v>
+      </c>
+      <c r="N64" s="13" t="str">
+        <f t="shared" si="20"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O64" s="13" t="str">
+        <f t="shared" si="20"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P64" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="Q64" s="14" t="s">
+        <v>341</v>
+      </c>
+      <c r="R64" s="14" t="s">
+        <v>342</v>
+      </c>
+      <c r="S64" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="T64" s="14" t="str">
+        <f t="shared" si="21"/>
+        <v>De API</v>
+      </c>
+      <c r="U64" s="14" t="str">
+        <f t="shared" si="21"/>
+        <v>Macros</v>
+      </c>
+      <c r="V64" s="60" t="str">
+        <f t="shared" si="21"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W64" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="X64" s="30" t="str">
+        <f t="shared" si="19"/>
+        <v>Key-Kml-64</v>
+      </c>
+      <c r="Y64" s="61" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z64" s="61" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA64" s="61" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB64" s="61" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC64" s="61" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD64" s="61" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="31">
+        <v>65</v>
+      </c>
+      <c r="B65" s="63" t="s">
+        <v>331</v>
+      </c>
+      <c r="C65" s="64" t="s">
+        <v>332</v>
+      </c>
+      <c r="D65" s="64" t="s">
+        <v>334</v>
+      </c>
+      <c r="E65" s="64" t="s">
+        <v>333</v>
+      </c>
+      <c r="F65" s="64" t="s">
+        <v>343</v>
+      </c>
+      <c r="G65" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="H65" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="I65" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="J65" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="K65" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="L65" s="13" t="str">
+        <f t="shared" si="20"/>
+        <v>De API</v>
+      </c>
+      <c r="M65" s="13" t="str">
+        <f t="shared" si="20"/>
+        <v>Macros</v>
+      </c>
+      <c r="N65" s="13" t="str">
+        <f t="shared" si="20"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O65" s="13" t="str">
+        <f t="shared" si="20"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P65" s="14" t="s">
+        <v>344</v>
+      </c>
+      <c r="Q65" s="14" t="s">
+        <v>345</v>
+      </c>
+      <c r="R65" s="14" t="s">
+        <v>346</v>
+      </c>
+      <c r="S65" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="T65" s="14" t="str">
+        <f t="shared" si="21"/>
+        <v>De API</v>
+      </c>
+      <c r="U65" s="14" t="str">
+        <f t="shared" si="21"/>
+        <v>Macros</v>
+      </c>
+      <c r="V65" s="60" t="str">
+        <f t="shared" si="21"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W65" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="X65" s="30" t="str">
+        <f t="shared" si="19"/>
+        <v>Key-Kml-65</v>
+      </c>
+      <c r="Y65" s="61" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z65" s="61" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA65" s="61" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB65" s="61" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC65" s="61" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD65" s="61" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="31">
+        <v>66</v>
+      </c>
+      <c r="B66" s="63" t="s">
+        <v>331</v>
+      </c>
+      <c r="C66" s="64" t="s">
+        <v>332</v>
+      </c>
+      <c r="D66" s="64" t="s">
+        <v>334</v>
+      </c>
+      <c r="E66" s="64" t="s">
+        <v>333</v>
+      </c>
+      <c r="F66" s="64" t="s">
+        <v>347</v>
+      </c>
+      <c r="G66" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="H66" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="I66" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="J66" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="K66" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="L66" s="13" t="str">
+        <f t="shared" si="20"/>
+        <v>De API</v>
+      </c>
+      <c r="M66" s="13" t="str">
+        <f t="shared" si="20"/>
+        <v>Macros</v>
+      </c>
+      <c r="N66" s="13" t="str">
+        <f t="shared" si="20"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O66" s="13" t="str">
+        <f t="shared" si="20"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P66" s="14" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q66" s="14" t="s">
+        <v>349</v>
+      </c>
+      <c r="R66" s="14" t="s">
+        <v>350</v>
+      </c>
+      <c r="S66" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="T66" s="14" t="str">
+        <f t="shared" si="21"/>
+        <v>De API</v>
+      </c>
+      <c r="U66" s="14" t="str">
+        <f t="shared" si="21"/>
+        <v>Macros</v>
+      </c>
+      <c r="V66" s="60" t="str">
+        <f t="shared" si="21"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W66" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="X66" s="30" t="str">
+        <f t="shared" si="19"/>
+        <v>Key-Kml-66</v>
+      </c>
+      <c r="Y66" s="61" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z66" s="61" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA66" s="61" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB66" s="61" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC66" s="61" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD66" s="61" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="31">
+        <v>67</v>
+      </c>
+      <c r="B67" s="63" t="s">
+        <v>331</v>
+      </c>
+      <c r="C67" s="64" t="s">
+        <v>332</v>
+      </c>
+      <c r="D67" s="64" t="s">
+        <v>334</v>
+      </c>
+      <c r="E67" s="64" t="s">
+        <v>351</v>
+      </c>
+      <c r="F67" s="64" t="s">
+        <v>352</v>
+      </c>
+      <c r="G67" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="H67" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="I67" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="J67" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="K67" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="L67" s="13" t="str">
+        <f t="shared" si="20"/>
+        <v>De API</v>
+      </c>
+      <c r="M67" s="13" t="str">
+        <f t="shared" si="20"/>
+        <v>Macros</v>
+      </c>
+      <c r="N67" s="13" t="str">
+        <f t="shared" si="20"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="O67" s="13" t="str">
+        <f t="shared" si="20"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P67" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="Q67" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="R67" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="S67" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="T67" s="14" t="str">
+        <f t="shared" si="21"/>
+        <v>De API</v>
+      </c>
+      <c r="U67" s="14" t="str">
+        <f t="shared" si="21"/>
+        <v>Macros</v>
+      </c>
+      <c r="V67" s="60" t="str">
+        <f t="shared" si="21"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="W67" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="X67" s="30" t="str">
+        <f t="shared" si="19"/>
+        <v>Key-Kml-67</v>
+      </c>
+      <c r="Y67" s="61" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z67" s="61" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA67" s="61" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB67" s="61" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC67" s="61" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD67" s="61" t="s">
         <v>2</v>
       </c>
     </row>
@@ -9034,29 +9487,27 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD62">
     <sortCondition ref="F30:F62"/>
   </sortState>
-  <conditionalFormatting sqref="A2:B63">
-    <cfRule type="cellIs" dxfId="32" priority="2" operator="equal">
+  <conditionalFormatting sqref="A2:B67">
+    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E67:F67">
+    <cfRule type="duplicateValues" dxfId="31" priority="2"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F1:F62">
-    <cfRule type="duplicateValues" dxfId="31" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F63">
-    <cfRule type="duplicateValues" dxfId="30" priority="3"/>
+  <conditionalFormatting sqref="F63:F66">
+    <cfRule type="duplicateValues" dxfId="29" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="29" priority="7" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R63">
-    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC1:AD1">
-    <cfRule type="cellIs" dxfId="27" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9068,15 +9519,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEE389E0-AD15-4DC4-98AC-F14614FE99CB}">
   <sheetPr codeName="Planilha16"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="13.1796875" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13.1640625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="3.36328125" style="22" customWidth="1"/>
-    <col min="2" max="10" width="7.6328125" style="23" customWidth="1"/>
-    <col min="11" max="21" width="7.6328125" style="21" customWidth="1"/>
-    <col min="22" max="16384" width="13.1796875" style="21"/>
+    <col min="1" max="1" width="3.33203125" style="22" customWidth="1"/>
+    <col min="2" max="10" width="7.6640625" style="23" customWidth="1"/>
+    <col min="11" max="21" width="7.6640625" style="21" customWidth="1"/>
+    <col min="22" max="16384" width="13.1640625" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="18" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="18" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="15" t="s">
         <v>66</v>
       </c>
@@ -9141,7 +9592,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A2" s="19">
         <v>2</v>
       </c>
@@ -9223,15 +9674,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{303D1F58-E12C-4CFF-B0CB-74B96F67AF9C}">
   <sheetPr codeName="Planilha17"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="10.6328125" defaultRowHeight="12" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.36328125" style="27" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.33203125" style="27" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7" style="28" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.36328125" style="28" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="12.81640625" style="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" style="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="12.83203125" style="28" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="24">
         <v>0</v>
       </c>
@@ -9254,7 +9705,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="10">
         <v>2</v>
       </c>
@@ -9305,30 +9756,30 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB5F366C-5F74-4E71-97A7-7194C8A394D8}">
   <dimension ref="A1:W23"/>
-  <sheetFormatPr defaultColWidth="6.1796875" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="6.1640625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.81640625" style="55" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.6328125" style="38" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" style="52" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="52" customWidth="1"/>
+    <col min="1" max="1" width="2.83203125" style="55" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" style="38" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" style="52" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="52" customWidth="1"/>
     <col min="5" max="5" width="8" style="52" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" style="52" customWidth="1"/>
-    <col min="7" max="7" width="8.6328125" style="52" customWidth="1"/>
-    <col min="8" max="8" width="5.6328125" style="52" customWidth="1"/>
-    <col min="9" max="9" width="5.36328125" style="52" customWidth="1"/>
-    <col min="10" max="10" width="8.453125" style="52" customWidth="1"/>
-    <col min="11" max="11" width="7.81640625" style="52" customWidth="1"/>
-    <col min="12" max="12" width="8.453125" style="52" customWidth="1"/>
-    <col min="13" max="13" width="8.36328125" style="52" customWidth="1"/>
-    <col min="14" max="14" width="5.81640625" style="52" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.1796875" style="52" customWidth="1"/>
+    <col min="6" max="6" width="12.1640625" style="52" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" style="52" customWidth="1"/>
+    <col min="8" max="8" width="5.6640625" style="52" customWidth="1"/>
+    <col min="9" max="9" width="5.33203125" style="52" customWidth="1"/>
+    <col min="10" max="10" width="8.5" style="52" customWidth="1"/>
+    <col min="11" max="11" width="7.83203125" style="52" customWidth="1"/>
+    <col min="12" max="12" width="8.5" style="52" customWidth="1"/>
+    <col min="13" max="13" width="8.33203125" style="52" customWidth="1"/>
+    <col min="14" max="14" width="5.83203125" style="52" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.1640625" style="52" customWidth="1"/>
     <col min="16" max="16" width="8" style="52" customWidth="1"/>
-    <col min="17" max="17" width="19.81640625" style="52" customWidth="1"/>
-    <col min="18" max="23" width="5.6328125" style="52" customWidth="1"/>
-    <col min="24" max="16384" width="6.1796875" style="52"/>
+    <col min="17" max="17" width="19.83203125" style="52" customWidth="1"/>
+    <col min="18" max="23" width="5.6640625" style="52" customWidth="1"/>
+    <col min="24" max="16384" width="6.1640625" style="52"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="40">
         <v>1</v>
       </c>
@@ -9399,15 +9850,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="45">
         <v>2</v>
       </c>
       <c r="B2" s="39" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C2" s="56" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D2" s="46" t="s">
         <v>2</v>
@@ -9440,10 +9891,10 @@
         <v>2</v>
       </c>
       <c r="N2" s="47" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O2" s="57" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P2" s="49" t="s">
         <v>2</v>
@@ -9470,21 +9921,21 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="45">
         <v>3</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C3" s="56" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D3" s="46" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E3" s="39" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F3" s="46" t="s">
         <v>2</v>
@@ -9511,10 +9962,10 @@
         <v>2</v>
       </c>
       <c r="N3" s="47" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O3" s="57" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P3" s="49" t="s">
         <v>2</v>
@@ -9541,21 +9992,21 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="45">
         <v>4</v>
       </c>
       <c r="B4" s="39" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C4" s="56" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D4" s="46" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E4" s="39" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F4" s="46" t="s">
         <v>2</v>
@@ -9582,10 +10033,10 @@
         <v>2</v>
       </c>
       <c r="N4" s="47" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O4" s="57" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P4" s="49" t="s">
         <v>2</v>
@@ -9612,21 +10063,21 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="45">
         <v>5</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C5" s="56" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D5" s="46" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E5" s="39" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F5" s="46" t="s">
         <v>2</v>
@@ -9653,10 +10104,10 @@
         <v>2</v>
       </c>
       <c r="N5" s="47" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O5" s="57" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P5" s="49" t="s">
         <v>2</v>
@@ -9683,22 +10134,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="45">
         <v>6</v>
       </c>
       <c r="B6" s="39" t="s">
+        <v>302</v>
+      </c>
+      <c r="C6" s="56" t="s">
+        <v>257</v>
+      </c>
+      <c r="D6" s="46" t="s">
+        <v>330</v>
+      </c>
+      <c r="E6" s="39" t="s">
         <v>303</v>
       </c>
-      <c r="C6" s="56" t="s">
-        <v>258</v>
-      </c>
-      <c r="D6" s="46" t="s">
-        <v>331</v>
-      </c>
-      <c r="E6" s="39" t="s">
-        <v>304</v>
-      </c>
       <c r="F6" s="46" t="s">
         <v>2</v>
       </c>
@@ -9724,10 +10175,10 @@
         <v>2</v>
       </c>
       <c r="N6" s="47" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O6" s="57" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="P6" s="49" t="s">
         <v>2</v>
@@ -9754,16 +10205,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="45">
         <v>7</v>
       </c>
       <c r="B7" s="39" t="s">
+        <v>303</v>
+      </c>
+      <c r="C7" s="56" t="s">
         <v>304</v>
       </c>
-      <c r="C7" s="56" t="s">
-        <v>305</v>
-      </c>
       <c r="D7" s="46" t="s">
         <v>2</v>
       </c>
@@ -9795,10 +10246,10 @@
         <v>2</v>
       </c>
       <c r="N7" s="47" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O7" s="57" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="P7" s="49" t="s">
         <v>2</v>
@@ -9825,21 +10276,21 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="45">
         <v>8</v>
       </c>
       <c r="B8" s="39" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C8" s="56" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D8" s="51" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E8" s="39" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F8" s="46" t="s">
         <v>2</v>
@@ -9866,10 +10317,10 @@
         <v>2</v>
       </c>
       <c r="N8" s="47" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O8" s="48" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P8" s="49" t="s">
         <v>2</v>
@@ -9896,28 +10347,28 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="45">
         <v>9</v>
       </c>
       <c r="B9" s="39" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C9" s="56" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D9" s="51" t="s">
+        <v>285</v>
+      </c>
+      <c r="E9" s="39" t="s">
+        <v>281</v>
+      </c>
+      <c r="F9" s="46" t="s">
+        <v>330</v>
+      </c>
+      <c r="G9" s="39" t="s">
         <v>286</v>
       </c>
-      <c r="E9" s="39" t="s">
-        <v>282</v>
-      </c>
-      <c r="F9" s="46" t="s">
-        <v>331</v>
-      </c>
-      <c r="G9" s="39" t="s">
-        <v>287</v>
-      </c>
       <c r="H9" s="46" t="s">
         <v>2</v>
       </c>
@@ -9937,10 +10388,10 @@
         <v>2</v>
       </c>
       <c r="N9" s="47" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O9" s="48" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P9" s="49" t="s">
         <v>2</v>
@@ -9967,27 +10418,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="45">
         <v>10</v>
       </c>
       <c r="B10" s="39" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C10" s="56" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D10" s="51" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E10" s="39" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F10" s="46" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H10" s="46" t="s">
         <v>2</v>
@@ -10008,10 +10459,10 @@
         <v>2</v>
       </c>
       <c r="N10" s="47" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O10" s="48" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P10" s="49" t="s">
         <v>2</v>
@@ -10038,27 +10489,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="45">
         <v>11</v>
       </c>
       <c r="B11" s="39" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C11" s="56" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D11" s="51" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E11" s="39" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F11" s="46" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H11" s="46" t="s">
         <v>2</v>
@@ -10079,10 +10530,10 @@
         <v>2</v>
       </c>
       <c r="N11" s="47" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O11" s="48" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P11" s="49" t="s">
         <v>2</v>
@@ -10109,27 +10560,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="45">
         <v>12</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C12" s="56" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D12" s="51" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E12" s="39" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F12" s="46" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H12" s="46" t="s">
         <v>2</v>
@@ -10138,28 +10589,28 @@
         <v>2</v>
       </c>
       <c r="J12" s="51" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="K12" s="39" t="s">
+        <v>302</v>
+      </c>
+      <c r="L12" s="51" t="s">
+        <v>285</v>
+      </c>
+      <c r="M12" s="39" t="s">
         <v>303</v>
       </c>
-      <c r="L12" s="51" t="s">
-        <v>286</v>
-      </c>
-      <c r="M12" s="39" t="s">
-        <v>304</v>
-      </c>
       <c r="N12" s="47" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O12" s="48" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P12" s="47" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q12" s="50" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R12" s="49" t="s">
         <v>2</v>
@@ -10180,27 +10631,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="45">
         <v>13</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C13" s="56" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D13" s="51" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E13" s="39" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F13" s="46" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H13" s="46" t="s">
         <v>2</v>
@@ -10209,28 +10660,28 @@
         <v>2</v>
       </c>
       <c r="J13" s="51" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="K13" s="39" t="s">
+        <v>302</v>
+      </c>
+      <c r="L13" s="51" t="s">
+        <v>285</v>
+      </c>
+      <c r="M13" s="39" t="s">
         <v>303</v>
       </c>
-      <c r="L13" s="51" t="s">
-        <v>286</v>
-      </c>
-      <c r="M13" s="39" t="s">
-        <v>304</v>
-      </c>
       <c r="N13" s="47" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O13" s="48" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P13" s="47" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q13" s="50" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R13" s="49" t="s">
         <v>2</v>
@@ -10251,27 +10702,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="45">
         <v>14</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C14" s="56" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D14" s="51" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E14" s="39" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F14" s="46" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H14" s="46" t="s">
         <v>2</v>
@@ -10280,28 +10731,28 @@
         <v>2</v>
       </c>
       <c r="J14" s="51" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="K14" s="39" t="s">
+        <v>302</v>
+      </c>
+      <c r="L14" s="51" t="s">
+        <v>285</v>
+      </c>
+      <c r="M14" s="39" t="s">
         <v>303</v>
       </c>
-      <c r="L14" s="51" t="s">
-        <v>286</v>
-      </c>
-      <c r="M14" s="39" t="s">
-        <v>304</v>
-      </c>
       <c r="N14" s="47" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O14" s="48" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P14" s="47" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q14" s="50" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R14" s="49" t="s">
         <v>2</v>
@@ -10322,27 +10773,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="45">
         <v>15</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C15" s="56" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D15" s="51" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E15" s="39" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F15" s="46" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G15" s="39" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H15" s="46" t="s">
         <v>2</v>
@@ -10351,28 +10802,28 @@
         <v>2</v>
       </c>
       <c r="J15" s="51" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="K15" s="39" t="s">
+        <v>302</v>
+      </c>
+      <c r="L15" s="51" t="s">
+        <v>285</v>
+      </c>
+      <c r="M15" s="39" t="s">
         <v>303</v>
       </c>
-      <c r="L15" s="51" t="s">
-        <v>286</v>
-      </c>
-      <c r="M15" s="39" t="s">
-        <v>304</v>
-      </c>
       <c r="N15" s="47" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O15" s="48" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P15" s="47" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q15" s="50" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R15" s="49" t="s">
         <v>2</v>
@@ -10393,27 +10844,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="45">
         <v>16</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C16" s="56" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D16" s="51" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E16" s="39" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F16" s="46" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G16" s="39" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H16" s="46" t="s">
         <v>2</v>
@@ -10422,28 +10873,28 @@
         <v>2</v>
       </c>
       <c r="J16" s="51" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="K16" s="39" t="s">
+        <v>302</v>
+      </c>
+      <c r="L16" s="51" t="s">
+        <v>285</v>
+      </c>
+      <c r="M16" s="39" t="s">
         <v>303</v>
       </c>
-      <c r="L16" s="51" t="s">
-        <v>286</v>
-      </c>
-      <c r="M16" s="39" t="s">
-        <v>304</v>
-      </c>
       <c r="N16" s="47" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O16" s="48" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P16" s="47" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q16" s="50" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R16" s="49" t="s">
         <v>2</v>
@@ -10464,27 +10915,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="45">
         <v>17</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C17" s="56" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D17" s="51" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E17" s="39" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F17" s="46" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G17" s="39" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H17" s="46" t="s">
         <v>2</v>
@@ -10493,28 +10944,28 @@
         <v>2</v>
       </c>
       <c r="J17" s="51" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="K17" s="39" t="s">
+        <v>302</v>
+      </c>
+      <c r="L17" s="51" t="s">
+        <v>285</v>
+      </c>
+      <c r="M17" s="39" t="s">
         <v>303</v>
       </c>
-      <c r="L17" s="51" t="s">
-        <v>286</v>
-      </c>
-      <c r="M17" s="39" t="s">
-        <v>304</v>
-      </c>
       <c r="N17" s="47" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O17" s="48" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P17" s="47" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q17" s="50" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R17" s="49" t="s">
         <v>2</v>
@@ -10535,57 +10986,57 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="45">
         <v>18</v>
       </c>
       <c r="B18" s="39" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C18" s="56" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D18" s="51" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E18" s="39" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F18" s="46" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G18" s="39" t="s">
+        <v>301</v>
+      </c>
+      <c r="H18" s="46" t="s">
+        <v>2</v>
+      </c>
+      <c r="I18" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="J18" s="51" t="s">
+        <v>285</v>
+      </c>
+      <c r="K18" s="39" t="s">
         <v>302</v>
       </c>
-      <c r="H18" s="46" t="s">
-        <v>2</v>
-      </c>
-      <c r="I18" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="J18" s="51" t="s">
-        <v>286</v>
-      </c>
-      <c r="K18" s="39" t="s">
+      <c r="L18" s="51" t="s">
+        <v>285</v>
+      </c>
+      <c r="M18" s="39" t="s">
         <v>303</v>
       </c>
-      <c r="L18" s="51" t="s">
-        <v>286</v>
-      </c>
-      <c r="M18" s="39" t="s">
-        <v>304</v>
-      </c>
       <c r="N18" s="47" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O18" s="48" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="P18" s="47" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q18" s="50" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R18" s="49" t="s">
         <v>2</v>
@@ -10606,57 +11057,57 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="45">
         <v>19</v>
       </c>
       <c r="B19" s="39" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C19" s="56" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D19" s="51" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E19" s="39" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F19" s="46" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G19" s="39" t="s">
+        <v>301</v>
+      </c>
+      <c r="H19" s="46" t="s">
+        <v>2</v>
+      </c>
+      <c r="I19" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="J19" s="51" t="s">
+        <v>285</v>
+      </c>
+      <c r="K19" s="39" t="s">
         <v>302</v>
       </c>
-      <c r="H19" s="46" t="s">
-        <v>2</v>
-      </c>
-      <c r="I19" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="J19" s="51" t="s">
-        <v>286</v>
-      </c>
-      <c r="K19" s="39" t="s">
+      <c r="L19" s="51" t="s">
+        <v>285</v>
+      </c>
+      <c r="M19" s="39" t="s">
         <v>303</v>
       </c>
-      <c r="L19" s="51" t="s">
-        <v>286</v>
-      </c>
-      <c r="M19" s="39" t="s">
-        <v>304</v>
-      </c>
       <c r="N19" s="47" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O19" s="48" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="P19" s="47" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q19" s="50" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R19" s="49" t="s">
         <v>2</v>
@@ -10677,57 +11128,57 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="45">
         <v>20</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C20" s="56" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D20" s="51" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E20" s="39" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F20" s="46" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G20" s="39" t="s">
+        <v>301</v>
+      </c>
+      <c r="H20" s="46" t="s">
+        <v>2</v>
+      </c>
+      <c r="I20" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="J20" s="51" t="s">
+        <v>285</v>
+      </c>
+      <c r="K20" s="39" t="s">
         <v>302</v>
       </c>
-      <c r="H20" s="46" t="s">
-        <v>2</v>
-      </c>
-      <c r="I20" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="J20" s="51" t="s">
-        <v>286</v>
-      </c>
-      <c r="K20" s="39" t="s">
+      <c r="L20" s="51" t="s">
+        <v>285</v>
+      </c>
+      <c r="M20" s="39" t="s">
         <v>303</v>
       </c>
-      <c r="L20" s="51" t="s">
-        <v>286</v>
-      </c>
-      <c r="M20" s="39" t="s">
-        <v>304</v>
-      </c>
       <c r="N20" s="47" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O20" s="48" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="P20" s="47" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q20" s="50" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R20" s="49" t="s">
         <v>2</v>
@@ -10748,57 +11199,57 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="45">
         <v>21</v>
       </c>
       <c r="B21" s="39" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C21" s="56" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D21" s="51" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E21" s="39" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F21" s="46" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G21" s="39" t="s">
+        <v>301</v>
+      </c>
+      <c r="H21" s="46" t="s">
+        <v>2</v>
+      </c>
+      <c r="I21" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="J21" s="51" t="s">
+        <v>285</v>
+      </c>
+      <c r="K21" s="39" t="s">
         <v>302</v>
       </c>
-      <c r="H21" s="46" t="s">
-        <v>2</v>
-      </c>
-      <c r="I21" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="J21" s="51" t="s">
-        <v>286</v>
-      </c>
-      <c r="K21" s="39" t="s">
+      <c r="L21" s="51" t="s">
+        <v>285</v>
+      </c>
+      <c r="M21" s="39" t="s">
         <v>303</v>
       </c>
-      <c r="L21" s="51" t="s">
-        <v>286</v>
-      </c>
-      <c r="M21" s="39" t="s">
-        <v>304</v>
-      </c>
       <c r="N21" s="47" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O21" s="48" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="P21" s="47" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q21" s="50" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R21" s="49" t="s">
         <v>2</v>
@@ -10819,57 +11270,57 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="45">
         <v>22</v>
       </c>
       <c r="B22" s="39" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C22" s="56" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D22" s="51" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E22" s="39" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F22" s="46" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G22" s="39" t="s">
+        <v>301</v>
+      </c>
+      <c r="H22" s="46" t="s">
+        <v>2</v>
+      </c>
+      <c r="I22" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="J22" s="51" t="s">
+        <v>285</v>
+      </c>
+      <c r="K22" s="39" t="s">
         <v>302</v>
       </c>
-      <c r="H22" s="46" t="s">
-        <v>2</v>
-      </c>
-      <c r="I22" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="J22" s="51" t="s">
-        <v>286</v>
-      </c>
-      <c r="K22" s="39" t="s">
+      <c r="L22" s="51" t="s">
+        <v>285</v>
+      </c>
+      <c r="M22" s="39" t="s">
         <v>303</v>
       </c>
-      <c r="L22" s="51" t="s">
-        <v>286</v>
-      </c>
-      <c r="M22" s="39" t="s">
-        <v>304</v>
-      </c>
       <c r="N22" s="47" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O22" s="48" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P22" s="47" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q22" s="50" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R22" s="49" t="s">
         <v>2</v>
@@ -10890,57 +11341,57 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="45">
         <v>23</v>
       </c>
       <c r="B23" s="39" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C23" s="56" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D23" s="51" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E23" s="39" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F23" s="46" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G23" s="39" t="s">
+        <v>301</v>
+      </c>
+      <c r="H23" s="46" t="s">
+        <v>2</v>
+      </c>
+      <c r="I23" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="J23" s="51" t="s">
+        <v>285</v>
+      </c>
+      <c r="K23" s="39" t="s">
         <v>302</v>
       </c>
-      <c r="H23" s="46" t="s">
-        <v>2</v>
-      </c>
-      <c r="I23" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="J23" s="51" t="s">
-        <v>286</v>
-      </c>
-      <c r="K23" s="39" t="s">
+      <c r="L23" s="51" t="s">
+        <v>285</v>
+      </c>
+      <c r="M23" s="39" t="s">
         <v>303</v>
       </c>
-      <c r="L23" s="51" t="s">
-        <v>286</v>
-      </c>
-      <c r="M23" s="39" t="s">
-        <v>304</v>
-      </c>
       <c r="N23" s="47" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O23" s="48" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="P23" s="47" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q23" s="50" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R23" s="49" t="s">
         <v>2</v>

--- a/Versão5/GIS/Ontologia_Kml_2x2.xlsx
+++ b/Versão5/GIS/Ontologia_Kml_2x2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\GIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC37ADF8-9E6D-458B-B428-7DBB5CF02FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1FAD756-4834-4430-BCE4-80ADBCADA425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="681" activeTab="1" xr2:uid="{EADD6BF3-7ABC-4ACF-B5B1-0F5DE0265229}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="681" xr2:uid="{EADD6BF3-7ABC-4ACF-B5B1-0F5DE0265229}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="16" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1926" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2001" uniqueCount="405">
   <si>
     <t>Organização</t>
   </si>
@@ -114,34 +114,13 @@
     <t>Escola Politécnica da UFRJ</t>
   </si>
   <si>
-    <t>NormaNúmero</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
-    <t>Edição</t>
-  </si>
-  <si>
-    <t>ISBN</t>
-  </si>
-  <si>
-    <t>NormaEscopo</t>
-  </si>
-  <si>
-    <t>NormaReferência1</t>
-  </si>
-  <si>
-    <t>NormaReferência2</t>
-  </si>
-  <si>
     <t>Observações</t>
   </si>
   <si>
     <t>DataHora</t>
-  </si>
-  <si>
-    <t>Advertência1</t>
   </si>
   <si>
     <t>Algumas traduções podem precisar de revisão - Traducción al español incorporada</t>
@@ -348,9 +327,6 @@
     <t>0-CategoriaEquivalente</t>
   </si>
   <si>
-    <t>Link do Esquema</t>
-  </si>
-  <si>
     <t>Conceitos</t>
   </si>
   <si>
@@ -1071,18 +1047,6 @@
     <t>é.marcador.interno.de</t>
   </si>
   <si>
-    <t>Projeto</t>
-  </si>
-  <si>
-    <t>De.API</t>
-  </si>
-  <si>
-    <t>Métodos</t>
-  </si>
-  <si>
-    <t>Macros</t>
-  </si>
-  <si>
     <t>Função.Auxiliar</t>
   </si>
   <si>
@@ -1131,9 +1095,6 @@
     <t>Define a Function to filter objects in an application</t>
   </si>
   <si>
-    <t>Códigos.Visuais</t>
-  </si>
-  <si>
     <t>Bloco.de.Código</t>
   </si>
   <si>
@@ -1144,6 +1105,192 @@
   </si>
   <si>
     <t>Defines a Code written in visual programming systems</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>API.Plataforma</t>
+  </si>
+  <si>
+    <t>API.Macros</t>
+  </si>
+  <si>
+    <t>API.Método</t>
+  </si>
+  <si>
+    <t>API.Macros.Visuais</t>
+  </si>
+  <si>
+    <t>API.Método.Visual</t>
+  </si>
+  <si>
+    <t>Norma-Número</t>
+  </si>
+  <si>
+    <t>Norma-Edição</t>
+  </si>
+  <si>
+    <t>Norma-ISBN</t>
+  </si>
+  <si>
+    <t>Norma-Escopo</t>
+  </si>
+  <si>
+    <t>Norma-Referência-01</t>
+  </si>
+  <si>
+    <t>Norma-Referência-02</t>
+  </si>
+  <si>
+    <t>Norma-Referência-03</t>
+  </si>
+  <si>
+    <t>Advertência</t>
+  </si>
+  <si>
+    <t>Aviso</t>
+  </si>
+  <si>
+    <t>Alert</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-01</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-02</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-03</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-04</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-01</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-02</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-03</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-04</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-05</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-06</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-07</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-08</t>
+  </si>
+  <si>
+    <t>Fonte-SINAPI</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-01</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-02</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-03</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-04</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-01</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-02</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-03</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-04</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-05</t>
+  </si>
+  <si>
+    <t>Fonte-Bombeiros-01</t>
+  </si>
+  <si>
+    <t>https://brasil.un.org/pt-br/sdgs</t>
+  </si>
+  <si>
+    <t>https://eaesp.fgv.br/centros/centro-estudos-sustentabilidade/projetos/programa-brasileiro-ghg-protocol</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/acesso-a-informacao/acoes-e-programas/transformacao-ecologica/transformacao-ecologica</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/orgaos/spe/taxonomia-sustentavel-brasileira/cadernos</t>
+  </si>
+  <si>
+    <t>https://museunacional.ufrj.br/hortobotanico</t>
+  </si>
+  <si>
+    <t>https://www.embrapa.br/florestas/publicacoes</t>
+  </si>
+  <si>
+    <t>https://www.arvoresgigantes.org</t>
+  </si>
+  <si>
+    <t>https://www.scielo.br/j/abb</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/inpa/pt-br/Pesquisa/colecoes/botanica</t>
+  </si>
+  <si>
+    <t>https://botanicasaopaulo.org</t>
+  </si>
+  <si>
+    <t>https://pesquisa.in.gov.br/imprensa</t>
+  </si>
+  <si>
+    <t>https://mapas.florestal.gov.br</t>
+  </si>
+  <si>
+    <t>https://www.caixa.gov.br/site/Paginas/downloads.aspx#categoria_888</t>
+  </si>
+  <si>
+    <t>https://somasus.saude.gov.br/sistema/home</t>
+  </si>
+  <si>
+    <t>https://anvisalegis.datalegis.net</t>
+  </si>
+  <si>
+    <t>RDC 611/2022. Radiologia diagnóstica. Blindagem, proteção radiológica.</t>
+  </si>
+  <si>
+    <t>RDC 222/2018. Gerenciamento de resíduos. Plano de gerenciamento obrigatório.</t>
+  </si>
+  <si>
+    <t>NBR 9050. Acessibilidade. Todos os ambientes de uso público.</t>
+  </si>
+  <si>
+    <t>NBR 7256. Climatização em EAS. Obrigatória para CC, CTI, CME, hemodinâmica.</t>
+  </si>
+  <si>
+    <t>NBR 15575. Desempenho de edificações. Conforto térmico, acústico, lumínico.</t>
+  </si>
+  <si>
+    <t>NBR 13534. Instalações elétricas em EAS. Circuitos, aterramento, emergência.</t>
+  </si>
+  <si>
+    <t>NBR 12188. Gases medicinais. Centrais, redes, pontos de uso.</t>
+  </si>
+  <si>
+    <t>Segurança contra incêndio. Varia por estado, consultar regulamento local.</t>
   </si>
 </sst>
 </file>
@@ -1242,7 +1389,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="26">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1393,6 +1540,12 @@
         <bgColor rgb="FFFEF2CB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -1481,7 +1634,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1662,14 +1815,44 @@
     <xf numFmtId="0" fontId="7" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2360,15 +2543,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{643CFCF6-0637-46A8-9CC0-1BF6FB3A6D15}">
   <sheetPr codeName="Planilha14"/>
-  <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:C49"/>
+  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.5" customWidth="1"/>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="65.33203125" style="29" customWidth="1"/>
     <col min="3" max="3" width="4.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -2379,7 +2562,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
@@ -2390,18 +2573,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>13</v>
       </c>
@@ -2412,7 +2595,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>15</v>
       </c>
@@ -2424,7 +2607,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>16</v>
       </c>
@@ -2436,7 +2619,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>17</v>
       </c>
@@ -2447,7 +2630,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>19</v>
       </c>
@@ -2458,7 +2641,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>0</v>
       </c>
@@ -2469,177 +2652,459 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>23</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>24</v>
+        <v>350</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>25</v>
+        <v>351</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>26</v>
+        <v>352</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>27</v>
+        <v>353</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>28</v>
+        <v>354</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>90</v>
+        <v>355</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B18" s="7">
         <f ca="1">NOW()</f>
-        <v>46268.698208912036</v>
+        <v>46276.4347380787</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>31</v>
+        <v>356</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="5" t="s">
-        <v>33</v>
+    <row r="20" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="6" t="s">
+        <v>357</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
-        <v>34</v>
+    <row r="21" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="6" t="s">
+        <v>358</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>212</v>
+        <v>26</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B23" s="8" t="str">
-        <f>_xlfn.TRANSLATE(B22,"pt","es")</f>
+        <v>27</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="8" t="str">
+        <f>_xlfn.TRANSLATE(B24,"pt","es")</f>
         <v>Formalizar los elementos del proyecto BIM en formato KML 2.2</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="8" t="str">
-        <f>_xlfn.TRANSLATE(B22,"pt","en")</f>
+      <c r="C25" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="8" t="str">
+        <f>_xlfn.TRANSLATE(B24,"pt","en")</f>
         <v>Formalize BIM project elements in KML 2.2 format</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>39</v>
+      <c r="C26" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="B27" s="67" t="s">
+        <v>382</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="B28" s="68" t="s">
+        <v>383</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="B29" s="68" t="s">
+        <v>384</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="B30" s="69" t="s">
+        <v>385</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="B31" s="70" t="s">
+        <v>386</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="B32" s="70" t="s">
+        <v>387</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="B33" s="70" t="s">
+        <v>388</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="B34" s="71" t="s">
+        <v>389</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="B35" s="71" t="s">
+        <v>390</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="B36" s="70" t="s">
+        <v>391</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="B37" s="71" t="s">
+        <v>392</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="B38" s="70" t="s">
+        <v>393</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="B39" s="72" t="s">
+        <v>394</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="B40" s="72" t="s">
+        <v>395</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="B41" s="73" t="s">
+        <v>396</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="B42" s="74" t="s">
+        <v>397</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="B43" s="74" t="s">
+        <v>398</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="B44" s="74" t="s">
+        <v>399</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="B45" s="74" t="s">
+        <v>400</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="B46" s="74" t="s">
+        <v>401</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="B47" s="74" t="s">
+        <v>402</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="B48" s="74" t="s">
+        <v>403</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="B49" s="74" t="s">
+        <v>404</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B16" r:id="rId1" xr:uid="{85F79A7A-4111-4BD8-A3C5-4FD730DA4627}"/>
+    <hyperlink ref="B27" r:id="rId2" xr:uid="{9FEA7636-61F2-4698-8989-493E87B51FB6}"/>
+    <hyperlink ref="B29" r:id="rId3" xr:uid="{0EACB81A-CD0B-44F3-A416-60E982DA6D8E}"/>
+    <hyperlink ref="B28" r:id="rId4" xr:uid="{CF8E3DD9-8E89-4545-A417-82F341DBE1D9}"/>
+    <hyperlink ref="B39" r:id="rId5" location="categoria_888" xr:uid="{FBCA3707-7DFD-4BA9-87A9-DB9034CEE1DC}"/>
+    <hyperlink ref="B40" r:id="rId6" xr:uid="{864A0BE2-1486-4C4D-9E68-1AC3024FE332}"/>
+    <hyperlink ref="B41" r:id="rId7" xr:uid="{A3E46F5A-0D8C-4DB6-8B00-199A1482A6C1}"/>
+    <hyperlink ref="B30" r:id="rId8" xr:uid="{2EC06622-D1A1-463D-8AEE-A8D34A81746F}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -2648,31 +3113,36 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B21B10B-C8BF-4318-B9A8-B9240E89A4C8}">
   <dimension ref="A1:AD67"/>
-  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="2.83203125" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.5" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" customWidth="1"/>
-    <col min="4" max="4" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5" customWidth="1"/>
-    <col min="6" max="6" width="19.5" customWidth="1"/>
-    <col min="7" max="11" width="7.83203125" customWidth="1"/>
-    <col min="12" max="12" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="155.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="144.83203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="134.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" customWidth="1"/>
+    <col min="6" max="6" width="18.33203125" customWidth="1"/>
+    <col min="7" max="7" width="7.5" customWidth="1"/>
+    <col min="8" max="8" width="7.33203125" customWidth="1"/>
+    <col min="9" max="9" width="8" customWidth="1"/>
+    <col min="10" max="10" width="8.1640625" customWidth="1"/>
+    <col min="11" max="11" width="7.5" customWidth="1"/>
+    <col min="12" max="12" width="9.83203125" customWidth="1"/>
+    <col min="13" max="13" width="9.5" customWidth="1"/>
+    <col min="14" max="14" width="10.6640625" customWidth="1"/>
+    <col min="15" max="15" width="18.33203125" customWidth="1"/>
+    <col min="16" max="16" width="245" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="240" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="236.83203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.1640625" style="66" customWidth="1"/>
     <col min="20" max="20" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="9" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="3.5" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="3.1640625" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2681,91 +3151,91 @@
         <v>1</v>
       </c>
       <c r="B1" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="K1" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="L1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="34" t="s">
+      <c r="M1" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="34" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="35" t="s">
+      <c r="N1" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="35" t="s">
+      <c r="O1" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="35" t="s">
+      <c r="P1" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="J1" s="35" t="s">
+      <c r="Q1" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="K1" s="35" t="s">
+      <c r="R1" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="S1" s="65" t="s">
+        <v>87</v>
+      </c>
+      <c r="T1" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="U1" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="V1" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="W1" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="X1" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="Y1" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="Z1" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA1" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="R1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="S1" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="T1" s="9" t="s">
+      <c r="AB1" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC1" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="U1" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="V1" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="W1" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="X1" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y1" s="33" t="s">
-        <v>60</v>
-      </c>
-      <c r="Z1" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="AA1" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB1" s="33" t="s">
-        <v>93</v>
-      </c>
-      <c r="AC1" s="9" t="s">
-        <v>62</v>
-      </c>
       <c r="AD1" s="9" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -2773,19 +3243,19 @@
         <v>2</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F2" s="36" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="G2" s="32" t="s">
         <v>2</v>
@@ -2819,7 +3289,7 @@
         <v>Kml.Arquivo</v>
       </c>
       <c r="P2" s="37" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="Q2" s="14" t="str">
         <f>_xlfn.TRANSLATE(P2,"pt","es")</f>
@@ -2829,7 +3299,7 @@
         <f t="shared" ref="R2:R33" si="4">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>The root grouping element of the KML file that contains the declaration of the namespaces and wraps all geographic content.</v>
       </c>
-      <c r="S2" s="14" t="s">
+      <c r="S2" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T2" s="14" t="str">
@@ -2845,7 +3315,7 @@
         <v>Kml.Arquivo</v>
       </c>
       <c r="W2" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X2" s="30" t="str">
         <f t="shared" ref="X2:X33" si="8">CONCATENATE("Key-Kml-",A2)</f>
@@ -2867,7 +3337,7 @@
         <v>2</v>
       </c>
       <c r="AD2" s="37" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -2875,19 +3345,19 @@
         <v>3</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F3" s="36" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="G3" s="32" t="s">
         <v>2</v>
@@ -2921,16 +3391,16 @@
         <v>Kml.Atributo</v>
       </c>
       <c r="P3" s="37" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="Q3" s="14" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="R3" s="14" t="str">
         <f t="shared" si="4"/>
         <v>Attribute to qualify a KML element.</v>
       </c>
-      <c r="S3" s="14" t="s">
+      <c r="S3" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T3" s="14" t="str">
@@ -2946,7 +3416,7 @@
         <v>Kml.Atributo</v>
       </c>
       <c r="W3" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X3" s="30" t="str">
         <f t="shared" si="8"/>
@@ -2968,7 +3438,7 @@
         <v>2</v>
       </c>
       <c r="AD3" s="37" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -2976,19 +3446,19 @@
         <v>4</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F4" s="36" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="G4" s="32" t="s">
         <v>2</v>
@@ -3022,7 +3492,7 @@
         <v>Kml.Box</v>
       </c>
       <c r="P4" s="37" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="Q4" s="14" t="str">
         <f t="shared" ref="Q4:Q19" si="9">_xlfn.TRANSLATE(P4,"pt","es")</f>
@@ -3032,7 +3502,7 @@
         <f t="shared" si="4"/>
         <v>KML element. Defines a region with 4 boundaries &lt;LatLonBox&gt;&lt;north&gt;37.80005&lt;/north&gt; &lt;south&gt;37.50005&lt;/south&gt; &lt;east&gt;120.373033&lt;/east&gt; &lt;west&gt;120.376033&lt;/west&gt; &lt;rotation&gt;0&lt;/rotation&gt;&lt;/LatLonBox&gt;</v>
       </c>
-      <c r="S4" s="14" t="s">
+      <c r="S4" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T4" s="14" t="str">
@@ -3048,7 +3518,7 @@
         <v>Kml.Box</v>
       </c>
       <c r="W4" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X4" s="30" t="str">
         <f t="shared" si="8"/>
@@ -3070,7 +3540,7 @@
         <v>2</v>
       </c>
       <c r="AD4" s="37" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3078,19 +3548,19 @@
         <v>5</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="G5" s="32" t="s">
         <v>2</v>
@@ -3124,7 +3594,7 @@
         <v>Kml.Box.Cardinal.Leste</v>
       </c>
       <c r="P5" s="37" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="Q5" s="14" t="str">
         <f t="shared" si="9"/>
@@ -3134,7 +3604,7 @@
         <f t="shared" si="4"/>
         <v>KML element. Sets the longitude of the eastern boundary of a region &lt;east&gt;120.373033&lt;/east&gt;</v>
       </c>
-      <c r="S5" s="14" t="s">
+      <c r="S5" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T5" s="14" t="str">
@@ -3150,7 +3620,7 @@
         <v>Kml.Box.Cardinal.Leste</v>
       </c>
       <c r="W5" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X5" s="30" t="str">
         <f t="shared" si="8"/>
@@ -3172,7 +3642,7 @@
         <v>2</v>
       </c>
       <c r="AD5" s="37" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3180,19 +3650,19 @@
         <v>6</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F6" s="36" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="G6" s="32" t="s">
         <v>2</v>
@@ -3226,7 +3696,7 @@
         <v>Kml.Box.Cardinal.Norte</v>
       </c>
       <c r="P6" s="37" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="Q6" s="14" t="str">
         <f t="shared" si="9"/>
@@ -3236,7 +3706,7 @@
         <f t="shared" si="4"/>
         <v>KML element. Sets the latitude of the northern boundary of a region &lt;north&gt;37.80005&lt;/north&gt;</v>
       </c>
-      <c r="S6" s="14" t="s">
+      <c r="S6" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T6" s="14" t="str">
@@ -3252,7 +3722,7 @@
         <v>Kml.Box.Cardinal.Norte</v>
       </c>
       <c r="W6" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X6" s="30" t="str">
         <f t="shared" si="8"/>
@@ -3274,7 +3744,7 @@
         <v>2</v>
       </c>
       <c r="AD6" s="37" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3282,19 +3752,19 @@
         <v>7</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F7" s="36" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="G7" s="32" t="s">
         <v>2</v>
@@ -3328,7 +3798,7 @@
         <v>Kml.Box.Cardinal.Oeste</v>
       </c>
       <c r="P7" s="37" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="Q7" s="14" t="str">
         <f t="shared" si="9"/>
@@ -3338,7 +3808,7 @@
         <f t="shared" si="4"/>
         <v>KML element. Defines the longitude of the western boundary of a region &lt;west&gt;120.376033&lt;/west&gt;</v>
       </c>
-      <c r="S7" s="14" t="s">
+      <c r="S7" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T7" s="14" t="str">
@@ -3354,7 +3824,7 @@
         <v>Kml.Box.Cardinal.Oeste</v>
       </c>
       <c r="W7" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X7" s="30" t="str">
         <f t="shared" si="8"/>
@@ -3376,7 +3846,7 @@
         <v>2</v>
       </c>
       <c r="AD7" s="37" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3384,19 +3854,19 @@
         <v>8</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F8" s="36" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="G8" s="32" t="s">
         <v>2</v>
@@ -3430,7 +3900,7 @@
         <v>Kml.Box.Cardinal.Sul</v>
       </c>
       <c r="P8" s="37" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="Q8" s="14" t="str">
         <f t="shared" si="9"/>
@@ -3440,7 +3910,7 @@
         <f t="shared" si="4"/>
         <v>KML element. Sets the latitude of the southern boundary of a region &lt;south&gt;37.50005&lt;/south&gt;</v>
       </c>
-      <c r="S8" s="14" t="s">
+      <c r="S8" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T8" s="14" t="str">
@@ -3456,7 +3926,7 @@
         <v>Kml.Box.Cardinal.Sul</v>
       </c>
       <c r="W8" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X8" s="30" t="str">
         <f t="shared" si="8"/>
@@ -3478,7 +3948,7 @@
         <v>2</v>
       </c>
       <c r="AD8" s="37" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3486,19 +3956,19 @@
         <v>9</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F9" s="36" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="G9" s="32" t="s">
         <v>2</v>
@@ -3532,7 +4002,7 @@
         <v>Kml.Box.Rotado</v>
       </c>
       <c r="P9" s="37" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="Q9" s="14" t="str">
         <f t="shared" si="9"/>
@@ -3542,7 +4012,7 @@
         <f t="shared" si="4"/>
         <v>KML element. Sets a &lt;rotation&gt;rotation 45&lt;/rotation&gt;</v>
       </c>
-      <c r="S9" s="14" t="s">
+      <c r="S9" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T9" s="14" t="str">
@@ -3558,7 +4028,7 @@
         <v>Kml.Box.Rotado</v>
       </c>
       <c r="W9" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X9" s="30" t="str">
         <f t="shared" si="8"/>
@@ -3580,7 +4050,7 @@
         <v>2</v>
       </c>
       <c r="AD9" s="37" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3588,19 +4058,19 @@
         <v>10</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F10" s="36" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="G10" s="32" t="s">
         <v>2</v>
@@ -3634,7 +4104,7 @@
         <v>Kml.Camara</v>
       </c>
       <c r="P10" s="37" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="Q10" s="14" t="str">
         <f t="shared" si="9"/>
@@ -3644,7 +4114,7 @@
         <f t="shared" si="4"/>
         <v>Visualization element in KML. Sets the exact position and orientation of the camera itself in three-dimensional space (latitude, longitude, altitude, rotation, and tilt).</v>
       </c>
-      <c r="S10" s="14" t="s">
+      <c r="S10" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T10" s="14" t="str">
@@ -3660,7 +4130,7 @@
         <v>Kml.Camara</v>
       </c>
       <c r="W10" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X10" s="30" t="str">
         <f t="shared" si="8"/>
@@ -3682,7 +4152,7 @@
         <v>2</v>
       </c>
       <c r="AD10" s="37" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3690,19 +4160,19 @@
         <v>11</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F11" s="36" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="G11" s="32" t="s">
         <v>2</v>
@@ -3736,7 +4206,7 @@
         <v>Kml.Camara.Alcance</v>
       </c>
       <c r="P11" s="37" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="Q11" s="14" t="str">
         <f t="shared" si="9"/>
@@ -3746,7 +4216,7 @@
         <f t="shared" si="4"/>
         <v>Specifies the focal length of the camera to the point of interest in meters. &lt;range&gt;1000&lt;/range&gt;</v>
       </c>
-      <c r="S11" s="14" t="s">
+      <c r="S11" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T11" s="14" t="str">
@@ -3762,7 +4232,7 @@
         <v>Kml.Camara.Alcance</v>
       </c>
       <c r="W11" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X11" s="30" t="str">
         <f t="shared" si="8"/>
@@ -3784,7 +4254,7 @@
         <v>2</v>
       </c>
       <c r="AD11" s="37" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3792,19 +4262,19 @@
         <v>12</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F12" s="36" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="G12" s="32" t="s">
         <v>2</v>
@@ -3838,7 +4308,7 @@
         <v>Kml.Camara.Alvo</v>
       </c>
       <c r="P12" s="37" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="Q12" s="14" t="str">
         <f t="shared" si="9"/>
@@ -3848,7 +4318,7 @@
         <f t="shared" si="4"/>
         <v>Visualization element in KML. Sets the view by positioning the camera relative to a target geographic point (including distance, tilt, and heading).</v>
       </c>
-      <c r="S12" s="14" t="s">
+      <c r="S12" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T12" s="14" t="str">
@@ -3864,7 +4334,7 @@
         <v>Kml.Camara.Alvo</v>
       </c>
       <c r="W12" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X12" s="30" t="str">
         <f t="shared" si="8"/>
@@ -3886,7 +4356,7 @@
         <v>2</v>
       </c>
       <c r="AD12" s="37" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3894,19 +4364,19 @@
         <v>13</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F13" s="36" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="G13" s="32" t="s">
         <v>2</v>
@@ -3940,7 +4410,7 @@
         <v>Kml.Camara.Azimut</v>
       </c>
       <c r="P13" s="37" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="Q13" s="14" t="str">
         <f t="shared" si="9"/>
@@ -3950,7 +4420,7 @@
         <f t="shared" si="4"/>
         <v>KML element. Sets the azimuth direction clockwise and in decimal degrees (North = 0, East = 90, South = 180, West = 270). &lt;heading&gt;0&lt;/heading&gt;</v>
       </c>
-      <c r="S13" s="14" t="s">
+      <c r="S13" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T13" s="14" t="str">
@@ -3966,7 +4436,7 @@
         <v>Kml.Camara.Azimut</v>
       </c>
       <c r="W13" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X13" s="30" t="str">
         <f t="shared" si="8"/>
@@ -3988,7 +4458,7 @@
         <v>2</v>
       </c>
       <c r="AD13" s="37" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3996,19 +4466,19 @@
         <v>14</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="G14" s="32" t="s">
         <v>2</v>
@@ -4042,7 +4512,7 @@
         <v>Kml.Dado.Estendido</v>
       </c>
       <c r="P14" s="37" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="Q14" s="14" t="str">
         <f t="shared" si="9"/>
@@ -4052,7 +4522,7 @@
         <f t="shared" si="4"/>
         <v>KML element. Defines an extended (custom) dataset. &lt;ExtendendData&gt; ..... &lt;/ExtendedData&gt;</v>
       </c>
-      <c r="S14" s="14" t="s">
+      <c r="S14" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T14" s="14" t="str">
@@ -4068,7 +4538,7 @@
         <v>Kml.Dado.Estendido</v>
       </c>
       <c r="W14" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X14" s="30" t="str">
         <f t="shared" si="8"/>
@@ -4090,7 +4560,7 @@
         <v>2</v>
       </c>
       <c r="AD14" s="37" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4098,19 +4568,19 @@
         <v>15</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F15" s="36" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="G15" s="32" t="s">
         <v>2</v>
@@ -4144,7 +4614,7 @@
         <v>Kml.Dado.Estendido.Dado</v>
       </c>
       <c r="P15" s="37" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="Q15" s="14" t="str">
         <f t="shared" si="9"/>
@@ -4154,7 +4624,7 @@
         <f t="shared" si="4"/>
         <v>KML element. Define a custom data within ExtendenData &lt;Data name='doname'&gt;&lt;value&gt;1&lt;/value&gt;&lt;/Data&gt;</v>
       </c>
-      <c r="S15" s="14" t="s">
+      <c r="S15" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T15" s="14" t="str">
@@ -4170,7 +4640,7 @@
         <v>Kml.Dado.Estendido.Dado</v>
       </c>
       <c r="W15" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X15" s="30" t="str">
         <f t="shared" si="8"/>
@@ -4192,7 +4662,7 @@
         <v>2</v>
       </c>
       <c r="AD15" s="37" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4200,19 +4670,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F16" s="36" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="G16" s="32" t="s">
         <v>2</v>
@@ -4246,7 +4716,7 @@
         <v>Kml.Dado.Estendido.Dado.Simples</v>
       </c>
       <c r="P16" s="37" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="Q16" s="14" t="str">
         <f t="shared" si="9"/>
@@ -4256,7 +4726,7 @@
         <f t="shared" si="4"/>
         <v>KML element. Define a custom flat data inside ExtendenData &lt;SimpleData name='Elevation'&gt;10000&lt;/SimpleData&gt;</v>
       </c>
-      <c r="S16" s="14" t="s">
+      <c r="S16" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T16" s="14" t="str">
@@ -4272,7 +4742,7 @@
         <v>Kml.Dado.Estendido.Dado.Simples</v>
       </c>
       <c r="W16" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X16" s="30" t="str">
         <f t="shared" si="8"/>
@@ -4294,7 +4764,7 @@
         <v>2</v>
       </c>
       <c r="AD16" s="37" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4302,19 +4772,19 @@
         <v>17</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F17" s="36" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="G17" s="32" t="s">
         <v>2</v>
@@ -4348,7 +4818,7 @@
         <v>Kml.Dado.Estendido.Esquema</v>
       </c>
       <c r="P17" s="37" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="Q17" s="14" t="str">
         <f t="shared" si="9"/>
@@ -4358,7 +4828,7 @@
         <f t="shared" si="4"/>
         <v>KML element. Define a custom layout &lt;Schema&gt; ..... &lt;/Schema&gt;</v>
       </c>
-      <c r="S17" s="14" t="s">
+      <c r="S17" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T17" s="14" t="str">
@@ -4374,7 +4844,7 @@
         <v>Kml.Dado.Estendido.Esquema</v>
       </c>
       <c r="W17" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X17" s="30" t="str">
         <f t="shared" si="8"/>
@@ -4396,7 +4866,7 @@
         <v>2</v>
       </c>
       <c r="AD17" s="37" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4404,19 +4874,19 @@
         <v>18</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F18" s="36" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="G18" s="32" t="s">
         <v>2</v>
@@ -4450,7 +4920,7 @@
         <v>Kml.Dado.Estendido.Esquema.Dado</v>
       </c>
       <c r="P18" s="37" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="Q18" s="14" t="str">
         <f t="shared" si="9"/>
@@ -4460,7 +4930,7 @@
         <f t="shared" si="4"/>
         <v>KML element. Defines a piece of data associated &lt;Schema&gt; with one to add typed custom data to a KML element.</v>
       </c>
-      <c r="S18" s="14" t="s">
+      <c r="S18" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T18" s="14" t="str">
@@ -4476,7 +4946,7 @@
         <v>Kml.Dado.Estendido.Esquema.Dado</v>
       </c>
       <c r="W18" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X18" s="30" t="str">
         <f t="shared" si="8"/>
@@ -4498,7 +4968,7 @@
         <v>2</v>
       </c>
       <c r="AD18" s="37" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4506,19 +4976,19 @@
         <v>19</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F19" s="36" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="G19" s="32" t="s">
         <v>2</v>
@@ -4552,7 +5022,7 @@
         <v>Kml.Documento</v>
       </c>
       <c r="P19" s="37" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="Q19" s="14" t="str">
         <f t="shared" si="9"/>
@@ -4562,7 +5032,7 @@
         <f t="shared" si="4"/>
         <v>KML bundler of geographic content, styles, and associated schemas. It is critical when the file contains multiple reusable objects or styles.</v>
       </c>
-      <c r="S19" s="14" t="s">
+      <c r="S19" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T19" s="14" t="str">
@@ -4578,7 +5048,7 @@
         <v>Kml.Documento</v>
       </c>
       <c r="W19" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X19" s="30" t="str">
         <f t="shared" si="8"/>
@@ -4600,7 +5070,7 @@
         <v>2</v>
       </c>
       <c r="AD19" s="37" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4608,19 +5078,19 @@
         <v>20</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F20" s="36" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="G20" s="32" t="s">
         <v>2</v>
@@ -4654,16 +5124,16 @@
         <v>Kml.Elemento.N0</v>
       </c>
       <c r="P20" s="37" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="Q20" s="37" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="R20" s="14" t="str">
         <f t="shared" si="4"/>
         <v>A KML element of level 0 Root (&lt;KML&gt;).</v>
       </c>
-      <c r="S20" s="14" t="s">
+      <c r="S20" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T20" s="14" t="str">
@@ -4679,7 +5149,7 @@
         <v>Kml.Elemento.N0</v>
       </c>
       <c r="W20" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X20" s="30" t="str">
         <f t="shared" si="8"/>
@@ -4701,7 +5171,7 @@
         <v>2</v>
       </c>
       <c r="AD20" s="37" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4709,19 +5179,19 @@
         <v>21</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F21" s="36" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="G21" s="32" t="s">
         <v>2</v>
@@ -4755,16 +5225,16 @@
         <v>Kml.Elemento.N1</v>
       </c>
       <c r="P21" s="37" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="Q21" s="37" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="R21" s="14" t="str">
         <f t="shared" si="4"/>
         <v>A level 1 KML element (&lt;Document&gt; and &lt;Folder&gt;).</v>
       </c>
-      <c r="S21" s="14" t="s">
+      <c r="S21" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T21" s="14" t="str">
@@ -4780,7 +5250,7 @@
         <v>Kml.Elemento.N1</v>
       </c>
       <c r="W21" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X21" s="30" t="str">
         <f t="shared" si="8"/>
@@ -4802,7 +5272,7 @@
         <v>2</v>
       </c>
       <c r="AD21" s="37" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4810,19 +5280,19 @@
         <v>22</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F22" s="36" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="G22" s="32" t="s">
         <v>2</v>
@@ -4856,16 +5326,16 @@
         <v>Kml.Elemento.N2</v>
       </c>
       <c r="P22" s="37" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="Q22" s="37" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="R22" s="14" t="str">
         <f t="shared" si="4"/>
         <v>A level 2 KML element (&lt;Placemark&gt;, &lt;GroundOverlay&gt;...).</v>
       </c>
-      <c r="S22" s="14" t="s">
+      <c r="S22" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T22" s="14" t="str">
@@ -4881,7 +5351,7 @@
         <v>Kml.Elemento.N2</v>
       </c>
       <c r="W22" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X22" s="30" t="str">
         <f t="shared" si="8"/>
@@ -4903,7 +5373,7 @@
         <v>2</v>
       </c>
       <c r="AD22" s="37" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4911,19 +5381,19 @@
         <v>23</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F23" s="36" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="G23" s="32" t="s">
         <v>2</v>
@@ -4957,16 +5427,16 @@
         <v>Kml.Elemento.N3</v>
       </c>
       <c r="P23" s="37" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="Q23" s="37" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="R23" s="14" t="str">
         <f t="shared" si="4"/>
         <v>A level 3 KML element (&lt;Point&gt;, &lt;Polygon&gt;, &lt;Style&gt;).</v>
       </c>
-      <c r="S23" s="14" t="s">
+      <c r="S23" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T23" s="14" t="str">
@@ -4982,7 +5452,7 @@
         <v>Kml.Elemento.N3</v>
       </c>
       <c r="W23" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X23" s="30" t="str">
         <f t="shared" si="8"/>
@@ -5004,7 +5474,7 @@
         <v>2</v>
       </c>
       <c r="AD23" s="37" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5012,19 +5482,19 @@
         <v>24</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F24" s="36" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="G24" s="32" t="s">
         <v>2</v>
@@ -5058,16 +5528,16 @@
         <v>Kml.Elemento.N4</v>
       </c>
       <c r="P24" s="37" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="Q24" s="37" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="R24" s="14" t="str">
         <f t="shared" si="4"/>
         <v>A level 4 KML element (&lt;Point&gt;, &lt;Polygon&gt;, &lt;Style&gt;).</v>
       </c>
-      <c r="S24" s="14" t="s">
+      <c r="S24" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T24" s="14" t="str">
@@ -5083,7 +5553,7 @@
         <v>Kml.Elemento.N4</v>
       </c>
       <c r="W24" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X24" s="30" t="str">
         <f t="shared" si="8"/>
@@ -5105,7 +5575,7 @@
         <v>2</v>
       </c>
       <c r="AD24" s="37" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5113,19 +5583,19 @@
         <v>25</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F25" s="36" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="G25" s="32" t="s">
         <v>2</v>
@@ -5159,16 +5629,16 @@
         <v>Kml.Elemento.N5</v>
       </c>
       <c r="P25" s="37" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="Q25" s="37" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="R25" s="14" t="str">
         <f t="shared" si="4"/>
         <v>A level 5 KML element (&lt;outerBoundaryIs&gt;, &lt;LinearRing&gt;, &lt;coordinates&gt;).</v>
       </c>
-      <c r="S25" s="14" t="s">
+      <c r="S25" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T25" s="14" t="str">
@@ -5184,7 +5654,7 @@
         <v>Kml.Elemento.N5</v>
       </c>
       <c r="W25" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X25" s="30" t="str">
         <f t="shared" si="8"/>
@@ -5206,7 +5676,7 @@
         <v>2</v>
       </c>
       <c r="AD25" s="37" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
     </row>
     <row r="26" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5214,19 +5684,19 @@
         <v>26</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F26" s="36" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="G26" s="32" t="s">
         <v>2</v>
@@ -5260,7 +5730,7 @@
         <v>Kml.Estilo</v>
       </c>
       <c r="P26" s="37" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="Q26" s="14" t="str">
         <f t="shared" ref="Q26:Q62" si="10">_xlfn.TRANSLATE(P26,"pt","es")</f>
@@ -5270,7 +5740,7 @@
         <f t="shared" si="4"/>
         <v>Styling element in KML. Groups graphical customization properties such as colors, transparencies, sizes, and icons.</v>
       </c>
-      <c r="S26" s="14" t="s">
+      <c r="S26" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T26" s="14" t="str">
@@ -5286,7 +5756,7 @@
         <v>Kml.Estilo</v>
       </c>
       <c r="W26" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X26" s="30" t="str">
         <f t="shared" si="8"/>
@@ -5308,7 +5778,7 @@
         <v>2</v>
       </c>
       <c r="AD26" s="37" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5316,19 +5786,19 @@
         <v>27</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F27" s="36" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="G27" s="32" t="s">
         <v>2</v>
@@ -5362,7 +5832,7 @@
         <v>Kml.Estilo.Balão</v>
       </c>
       <c r="P27" s="37" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="Q27" s="14" t="str">
         <f t="shared" si="10"/>
@@ -5372,7 +5842,7 @@
         <f t="shared" si="4"/>
         <v>Styling element in KML. Customizes the info/pop-up bubble that opens when you click on an element (supports HTML tags).</v>
       </c>
-      <c r="S27" s="14" t="s">
+      <c r="S27" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T27" s="14" t="str">
@@ -5388,7 +5858,7 @@
         <v>Kml.Estilo.Balão</v>
       </c>
       <c r="W27" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X27" s="30" t="str">
         <f t="shared" si="8"/>
@@ -5410,7 +5880,7 @@
         <v>2</v>
       </c>
       <c r="AD27" s="37" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5418,19 +5888,19 @@
         <v>28</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F28" s="36" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="G28" s="32" t="s">
         <v>2</v>
@@ -5464,7 +5934,7 @@
         <v>Kml.Estilo.Cor</v>
       </c>
       <c r="P28" s="37" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="Q28" s="14" t="str">
         <f t="shared" si="10"/>
@@ -5474,7 +5944,7 @@
         <f t="shared" si="4"/>
         <v>KML element. Sets a &lt;color&gt;color 7f0000ff&lt;/color&gt;</v>
       </c>
-      <c r="S28" s="14" t="s">
+      <c r="S28" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T28" s="14" t="str">
@@ -5490,7 +5960,7 @@
         <v>Kml.Estilo.Cor</v>
       </c>
       <c r="W28" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X28" s="30" t="str">
         <f t="shared" si="8"/>
@@ -5512,7 +5982,7 @@
         <v>2</v>
       </c>
       <c r="AD28" s="37" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5520,19 +5990,19 @@
         <v>29</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F29" s="36" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="G29" s="32" t="s">
         <v>2</v>
@@ -5566,7 +6036,7 @@
         <v>Kml.Estilo.Espessura</v>
       </c>
       <c r="P29" s="37" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="Q29" s="14" t="str">
         <f t="shared" si="10"/>
@@ -5576,7 +6046,7 @@
         <f t="shared" si="4"/>
         <v>KML element. Sets a thickness &lt;width&gt;of 1&lt;/width&gt;</v>
       </c>
-      <c r="S29" s="14" t="s">
+      <c r="S29" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T29" s="14" t="str">
@@ -5592,7 +6062,7 @@
         <v>Kml.Estilo.Espessura</v>
       </c>
       <c r="W29" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X29" s="30" t="str">
         <f t="shared" si="8"/>
@@ -5614,7 +6084,7 @@
         <v>2</v>
       </c>
       <c r="AD29" s="37" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
     </row>
     <row r="30" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5622,19 +6092,19 @@
         <v>30</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F30" s="36" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="G30" s="32" t="s">
         <v>2</v>
@@ -5668,7 +6138,7 @@
         <v>Kml.Estilo.Linha</v>
       </c>
       <c r="P30" s="37" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="Q30" s="14" t="str">
         <f t="shared" si="10"/>
@@ -5678,7 +6148,7 @@
         <f t="shared" si="4"/>
         <v>Styling element in KML. Sets the color, opacity, and thickness of the lines.</v>
       </c>
-      <c r="S30" s="14" t="s">
+      <c r="S30" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T30" s="14" t="str">
@@ -5694,7 +6164,7 @@
         <v>Kml.Estilo.Linha</v>
       </c>
       <c r="W30" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X30" s="30" t="str">
         <f t="shared" si="8"/>
@@ -5716,7 +6186,7 @@
         <v>2</v>
       </c>
       <c r="AD30" s="37" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5724,19 +6194,19 @@
         <v>31</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F31" s="36" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="G31" s="32" t="s">
         <v>2</v>
@@ -5770,7 +6240,7 @@
         <v>Kml.Estilo.Mapa</v>
       </c>
       <c r="P31" s="37" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="Q31" s="14" t="str">
         <f t="shared" si="10"/>
@@ -5780,7 +6250,7 @@
         <f t="shared" si="4"/>
         <v>Styling element in KML. Allows you to toggle the appearance of an element based on the user's action (e.g., change the icon when the cursor hovers).</v>
       </c>
-      <c r="S31" s="14" t="s">
+      <c r="S31" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T31" s="14" t="str">
@@ -5796,7 +6266,7 @@
         <v>Kml.Estilo.Mapa</v>
       </c>
       <c r="W31" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X31" s="30" t="str">
         <f t="shared" si="8"/>
@@ -5818,7 +6288,7 @@
         <v>2</v>
       </c>
       <c r="AD31" s="37" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="32" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5826,19 +6296,19 @@
         <v>32</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F32" s="36" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="G32" s="32" t="s">
         <v>2</v>
@@ -5872,7 +6342,7 @@
         <v>Kml.Estilo.Texto</v>
       </c>
       <c r="P32" s="37" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="Q32" s="14" t="str">
         <f t="shared" si="10"/>
@@ -5882,7 +6352,7 @@
         <f t="shared" si="4"/>
         <v>Styling element in KML. Sets the color and scale of the bullet label text.</v>
       </c>
-      <c r="S32" s="14" t="s">
+      <c r="S32" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T32" s="14" t="str">
@@ -5898,7 +6368,7 @@
         <v>Kml.Estilo.Texto</v>
       </c>
       <c r="W32" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X32" s="30" t="str">
         <f t="shared" si="8"/>
@@ -5920,7 +6390,7 @@
         <v>2</v>
       </c>
       <c r="AD32" s="37" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5928,19 +6398,19 @@
         <v>33</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F33" s="36" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="G33" s="32" t="s">
         <v>2</v>
@@ -5974,7 +6444,7 @@
         <v>Kml.Estilo.Usado</v>
       </c>
       <c r="P33" s="37" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="Q33" s="14" t="str">
         <f t="shared" si="10"/>
@@ -5984,7 +6454,7 @@
         <f t="shared" si="4"/>
         <v>KML element. Sets the reference to a style already defined &lt;styleUrl&gt;#EstilodeLinha&lt;/styleUrl&gt;</v>
       </c>
-      <c r="S33" s="14" t="s">
+      <c r="S33" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T33" s="14" t="str">
@@ -6000,7 +6470,7 @@
         <v>Kml.Estilo.Usado</v>
       </c>
       <c r="W33" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X33" s="30" t="str">
         <f t="shared" si="8"/>
@@ -6022,7 +6492,7 @@
         <v>2</v>
       </c>
       <c r="AD33" s="37" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="34" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6030,19 +6500,19 @@
         <v>34</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F34" s="36" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="G34" s="32" t="s">
         <v>2</v>
@@ -6060,7 +6530,7 @@
         <v>2</v>
       </c>
       <c r="L34" s="13" t="str">
-        <f t="shared" ref="L34:L62" si="11">CONCATENATE("", C34)</f>
+        <f t="shared" ref="L34:M63" si="11">CONCATENATE("", C34)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M34" s="13" t="str">
@@ -6076,7 +6546,7 @@
         <v>Kml.Estilo.Visibilidade</v>
       </c>
       <c r="P34" s="37" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="Q34" s="14" t="str">
         <f t="shared" si="10"/>
@@ -6086,7 +6556,7 @@
         <f t="shared" ref="R34:R62" si="15">_xlfn.TRANSLATE(P34,"pt","en")</f>
         <v>KML element. Sets a visibility mode &lt;gx:labelVisibility&gt; &lt;/gx:labelVisibility&gt;</v>
       </c>
-      <c r="S34" s="14" t="s">
+      <c r="S34" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T34" s="14" t="str">
@@ -6102,10 +6572,10 @@
         <v>Kml.Estilo.Visibilidade</v>
       </c>
       <c r="W34" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X34" s="30" t="str">
-        <f t="shared" ref="X34:X67" si="19">CONCATENATE("Key-Kml-",A34)</f>
+        <f t="shared" ref="X34:X62" si="19">CONCATENATE("Key-Kml-",A34)</f>
         <v>Key-Kml-34</v>
       </c>
       <c r="Y34" s="14" t="s">
@@ -6124,7 +6594,7 @@
         <v>2</v>
       </c>
       <c r="AD34" s="37" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
     </row>
     <row r="35" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6132,19 +6602,19 @@
         <v>35</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F35" s="36" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="G35" s="32" t="s">
         <v>2</v>
@@ -6178,7 +6648,7 @@
         <v>Kml.Extrusão</v>
       </c>
       <c r="P35" s="37" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="Q35" s="14" t="str">
         <f t="shared" si="10"/>
@@ -6188,7 +6658,7 @@
         <f t="shared" si="15"/>
         <v>KML element. Sets an extrusion value &lt;extrude&gt;of 1&lt;/extrude&gt;.</v>
       </c>
-      <c r="S35" s="14" t="s">
+      <c r="S35" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T35" s="14" t="str">
@@ -6204,7 +6674,7 @@
         <v>Kml.Extrusão</v>
       </c>
       <c r="W35" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X35" s="30" t="str">
         <f t="shared" si="19"/>
@@ -6226,7 +6696,7 @@
         <v>2</v>
       </c>
       <c r="AD35" s="37" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
     </row>
     <row r="36" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6234,19 +6704,19 @@
         <v>36</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F36" s="36" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="G36" s="32" t="s">
         <v>2</v>
@@ -6280,7 +6750,7 @@
         <v>Kml.Gira.X</v>
       </c>
       <c r="P36" s="37" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="Q36" s="14" t="str">
         <f t="shared" si="10"/>
@@ -6290,7 +6760,7 @@
         <f t="shared" si="15"/>
         <v>KML element. Sets the tilt about the X-axis &lt;tilt&gt;10.5&lt;/tilt&gt; A value of 0 view is downward toward the Earth. Value 90 the view is to the horizon. Value &gt; 90 indicates the view points up. The values are always positive.</v>
       </c>
-      <c r="S36" s="14" t="s">
+      <c r="S36" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T36" s="14" t="str">
@@ -6306,7 +6776,7 @@
         <v>Kml.Gira.X</v>
       </c>
       <c r="W36" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X36" s="30" t="str">
         <f t="shared" si="19"/>
@@ -6328,7 +6798,7 @@
         <v>2</v>
       </c>
       <c r="AD36" s="37" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="37" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6336,19 +6806,19 @@
         <v>37</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F37" s="36" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="G37" s="32" t="s">
         <v>2</v>
@@ -6382,7 +6852,7 @@
         <v>Kml.Gira.Z</v>
       </c>
       <c r="P37" s="37" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="Q37" s="14" t="str">
         <f t="shared" si="10"/>
@@ -6392,7 +6862,7 @@
         <f t="shared" si="15"/>
         <v>KML element. Defines a turn around the Z-axis &lt;roll&gt;0&lt;/roll&gt; cannot be negative value.</v>
       </c>
-      <c r="S37" s="14" t="s">
+      <c r="S37" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T37" s="14" t="str">
@@ -6408,7 +6878,7 @@
         <v>Kml.Gira.Z</v>
       </c>
       <c r="W37" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X37" s="30" t="str">
         <f t="shared" si="19"/>
@@ -6430,7 +6900,7 @@
         <v>2</v>
       </c>
       <c r="AD37" s="37" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
     </row>
     <row r="38" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6438,19 +6908,19 @@
         <v>38</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F38" s="36" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="G38" s="32" t="s">
         <v>2</v>
@@ -6484,7 +6954,7 @@
         <v>Kml.Lugar</v>
       </c>
       <c r="P38" s="37" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="Q38" s="14" t="str">
         <f t="shared" si="10"/>
@@ -6494,7 +6964,7 @@
         <f t="shared" si="15"/>
         <v>Geographic feature element in KML. Defines the most common element that represents an individual geographic feature and can associate a name, description, style, and geometry.</v>
       </c>
-      <c r="S38" s="14" t="s">
+      <c r="S38" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T38" s="14" t="str">
@@ -6510,7 +6980,7 @@
         <v>Kml.Lugar</v>
       </c>
       <c r="W38" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X38" s="30" t="str">
         <f t="shared" si="19"/>
@@ -6532,7 +7002,7 @@
         <v>2</v>
       </c>
       <c r="AD38" s="37" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="39" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6540,19 +7010,19 @@
         <v>39</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F39" s="36" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="G39" s="32" t="s">
         <v>2</v>
@@ -6586,7 +7056,7 @@
         <v>Kml.Lugar.Geometria</v>
       </c>
       <c r="P39" s="37" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="Q39" s="14" t="str">
         <f t="shared" si="10"/>
@@ -6596,7 +7066,7 @@
         <f t="shared" si="15"/>
         <v>Geographic feature element in KML. A container that groups several geometries under a single Placemark (for example, a country composed of several islands).</v>
       </c>
-      <c r="S39" s="14" t="s">
+      <c r="S39" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T39" s="14" t="str">
@@ -6612,7 +7082,7 @@
         <v>Kml.Lugar.Geometria</v>
       </c>
       <c r="W39" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X39" s="30" t="str">
         <f t="shared" si="19"/>
@@ -6634,7 +7104,7 @@
         <v>2</v>
       </c>
       <c r="AD39" s="37" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6642,19 +7112,19 @@
         <v>41</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F40" s="36" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="G40" s="32" t="s">
         <v>2</v>
@@ -6688,7 +7158,7 @@
         <v>Kml.Lugar.Ponto</v>
       </c>
       <c r="P40" s="37" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="Q40" s="14" t="str">
         <f t="shared" si="10"/>
@@ -6698,7 +7168,7 @@
         <f t="shared" si="15"/>
         <v>Geographic feature element in KML. Sets a point location on the map using longitude, latitude, and optionally altitude coordinates.</v>
       </c>
-      <c r="S40" s="14" t="s">
+      <c r="S40" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T40" s="14" t="str">
@@ -6714,7 +7184,7 @@
         <v>Kml.Lugar.Ponto</v>
       </c>
       <c r="W40" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X40" s="30" t="str">
         <f t="shared" si="19"/>
@@ -6736,7 +7206,7 @@
         <v>2</v>
       </c>
       <c r="AD40" s="37" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="41" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6744,19 +7214,19 @@
         <v>42</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F41" s="36" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="G41" s="32" t="s">
         <v>2</v>
@@ -6790,7 +7260,7 @@
         <v>Kml.Lugar.Ponto.Altitude</v>
       </c>
       <c r="P41" s="37" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="Q41" s="14" t="str">
         <f t="shared" si="10"/>
@@ -6800,7 +7270,7 @@
         <f t="shared" si="15"/>
         <v>KML element. Set an altitude &lt;altitude&gt;of 10.5&lt;/altitude&gt;</v>
       </c>
-      <c r="S41" s="14" t="s">
+      <c r="S41" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T41" s="14" t="str">
@@ -6816,7 +7286,7 @@
         <v>Kml.Lugar.Ponto.Altitude</v>
       </c>
       <c r="W41" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X41" s="30" t="str">
         <f t="shared" si="19"/>
@@ -6838,7 +7308,7 @@
         <v>2</v>
       </c>
       <c r="AD41" s="37" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
     </row>
     <row r="42" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6846,19 +7316,19 @@
         <v>43</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F42" s="36" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="G42" s="32" t="s">
         <v>2</v>
@@ -6892,7 +7362,7 @@
         <v>Kml.Lugar.Ponto.AltitudeModo</v>
       </c>
       <c r="P42" s="37" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="Q42" s="14" t="str">
         <f t="shared" si="10"/>
@@ -6902,7 +7372,7 @@
         <f t="shared" si="15"/>
         <v>KML element. Sets &lt;altitudeMode&gt;the absolute altitude&lt;/altitudeMode&gt; mode (Possible values: relativeToGround, clampToGround, and absolute)</v>
       </c>
-      <c r="S42" s="14" t="s">
+      <c r="S42" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T42" s="14" t="str">
@@ -6918,7 +7388,7 @@
         <v>Kml.Lugar.Ponto.AltitudeModo</v>
       </c>
       <c r="W42" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X42" s="30" t="str">
         <f t="shared" si="19"/>
@@ -6940,7 +7410,7 @@
         <v>2</v>
       </c>
       <c r="AD42" s="37" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
     </row>
     <row r="43" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6948,19 +7418,19 @@
         <v>44</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F43" s="36" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="G43" s="32" t="s">
         <v>2</v>
@@ -6994,7 +7464,7 @@
         <v>Kml.Lugar.Ponto.Latitude</v>
       </c>
       <c r="P43" s="37" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="Q43" s="14" t="str">
         <f t="shared" si="10"/>
@@ -7004,7 +7474,7 @@
         <f t="shared" si="15"/>
         <v>KML element. Sets latitude &lt;latitude&gt;-22.45&lt;/latitude&gt;</v>
       </c>
-      <c r="S43" s="14" t="s">
+      <c r="S43" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T43" s="14" t="str">
@@ -7020,7 +7490,7 @@
         <v>Kml.Lugar.Ponto.Latitude</v>
       </c>
       <c r="W43" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X43" s="30" t="str">
         <f t="shared" si="19"/>
@@ -7042,7 +7512,7 @@
         <v>2</v>
       </c>
       <c r="AD43" s="37" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
     </row>
     <row r="44" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7050,19 +7520,19 @@
         <v>45</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F44" s="36" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="G44" s="32" t="s">
         <v>2</v>
@@ -7096,7 +7566,7 @@
         <v>Kml.Lugar.Ponto.Longitude</v>
       </c>
       <c r="P44" s="37" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="Q44" s="14" t="str">
         <f t="shared" si="10"/>
@@ -7106,7 +7576,7 @@
         <f t="shared" si="15"/>
         <v>KML element. Sets longitude &lt;longitude&gt;-122.36415&lt;/longitude&gt;</v>
       </c>
-      <c r="S44" s="14" t="s">
+      <c r="S44" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T44" s="14" t="str">
@@ -7122,7 +7592,7 @@
         <v>Kml.Lugar.Ponto.Longitude</v>
       </c>
       <c r="W44" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X44" s="30" t="str">
         <f t="shared" si="19"/>
@@ -7144,7 +7614,7 @@
         <v>2</v>
       </c>
       <c r="AD44" s="37" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
     </row>
     <row r="45" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7152,19 +7622,19 @@
         <v>46</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F45" s="36" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="G45" s="32" t="s">
         <v>2</v>
@@ -7198,7 +7668,7 @@
         <v>Kml.Lugar.Ponto.XYZ</v>
       </c>
       <c r="P45" s="37" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="Q45" s="14" t="str">
         <f t="shared" si="10"/>
@@ -7208,7 +7678,7 @@
         <f t="shared" si="15"/>
         <v>Coordinate element in KML. Coordinates. X, Y, Z separated by commas and coordinated by spaces &lt;coordinates&gt;x1 , y1 , z1 x2 , y2 , z2 x3 , y3 , z3 x4 , y4 , z4&lt;/coordinates&gt;.</v>
       </c>
-      <c r="S45" s="14" t="s">
+      <c r="S45" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T45" s="14" t="str">
@@ -7224,7 +7694,7 @@
         <v>Kml.Lugar.Ponto.XYZ</v>
       </c>
       <c r="W45" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X45" s="30" t="str">
         <f t="shared" si="19"/>
@@ -7246,7 +7716,7 @@
         <v>2</v>
       </c>
       <c r="AD45" s="37" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="46" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7254,19 +7724,19 @@
         <v>47</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F46" s="36" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="G46" s="32" t="s">
         <v>2</v>
@@ -7300,7 +7770,7 @@
         <v>Kml.Lugar.Segmento</v>
       </c>
       <c r="P46" s="37" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="Q46" s="14" t="str">
         <f t="shared" si="10"/>
@@ -7310,7 +7780,7 @@
         <f t="shared" si="15"/>
         <v>Geographic feature element in KML. Defines a continuous line through a sequence of coordinates (useful for paths, routes, and rivers).</v>
       </c>
-      <c r="S46" s="14" t="s">
+      <c r="S46" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T46" s="14" t="str">
@@ -7326,7 +7796,7 @@
         <v>Kml.Lugar.Segmento</v>
       </c>
       <c r="W46" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X46" s="30" t="str">
         <f t="shared" si="19"/>
@@ -7348,7 +7818,7 @@
         <v>2</v>
       </c>
       <c r="AD46" s="37" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="47" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7356,19 +7826,19 @@
         <v>48</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F47" s="36" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="G47" s="32" t="s">
         <v>2</v>
@@ -7402,7 +7872,7 @@
         <v>Kml.Lugar.Segmento.Poligonal</v>
       </c>
       <c r="P47" s="37" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="Q47" s="14" t="str">
         <f t="shared" si="10"/>
@@ -7412,7 +7882,7 @@
         <f t="shared" si="15"/>
         <v>Geographic feature element in KML. A closed, non-self-intersecting line, used primarily to define the boundaries of a polygon.</v>
       </c>
-      <c r="S47" s="14" t="s">
+      <c r="S47" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T47" s="14" t="str">
@@ -7428,7 +7898,7 @@
         <v>Kml.Lugar.Segmento.Poligonal</v>
       </c>
       <c r="W47" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X47" s="30" t="str">
         <f t="shared" si="19"/>
@@ -7450,7 +7920,7 @@
         <v>2</v>
       </c>
       <c r="AD47" s="37" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="48" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7458,19 +7928,19 @@
         <v>49</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F48" s="36" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="G48" s="32" t="s">
         <v>2</v>
@@ -7504,7 +7974,7 @@
         <v>Kml.Lugar.Segmento.Poligono</v>
       </c>
       <c r="P48" s="37" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="Q48" s="14" t="str">
         <f t="shared" si="10"/>
@@ -7514,7 +7984,7 @@
         <f t="shared" si="15"/>
         <v>Geographic feature element in KML. Defines an area bounded by an outer boundary (&lt;outerBoundaryIs&gt;) and, optionally, inner boundary (&lt;innerBoundaryIs&gt;) to create holes.</v>
       </c>
-      <c r="S48" s="14" t="s">
+      <c r="S48" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T48" s="14" t="str">
@@ -7530,7 +8000,7 @@
         <v>Kml.Lugar.Segmento.Poligono</v>
       </c>
       <c r="W48" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X48" s="30" t="str">
         <f t="shared" si="19"/>
@@ -7552,7 +8022,7 @@
         <v>2</v>
       </c>
       <c r="AD48" s="37" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="49" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7560,19 +8030,19 @@
         <v>40</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F49" s="36" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="G49" s="32" t="s">
         <v>2</v>
@@ -7606,7 +8076,7 @@
         <v>Kml.Lugar.Segmento.Projeção</v>
       </c>
       <c r="P49" s="37" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="Q49" s="14" t="str">
         <f t="shared" si="10"/>
@@ -7616,7 +8086,7 @@
         <f t="shared" si="15"/>
         <v>Controls whether a line or polygon follows the curvature of the earth, the terrain reliefs, or whether it is drawn as a straight line in three-dimensional space. &lt;tessellate&gt;1&lt;/tessellate&gt; Works only if the altitude mode (&lt;altitudeMode&gt;) is set to clampToGround (secured to ground, which is the default). If the altitude is absolute or relative to the ground, the effect of tessellate is ignored.</v>
       </c>
-      <c r="S49" s="14" t="s">
+      <c r="S49" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T49" s="14" t="str">
@@ -7632,7 +8102,7 @@
         <v>Kml.Lugar.Segmento.Projeção</v>
       </c>
       <c r="W49" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X49" s="30" t="str">
         <f t="shared" si="19"/>
@@ -7654,7 +8124,7 @@
         <v>2</v>
       </c>
       <c r="AD49" s="37" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
     </row>
     <row r="50" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7662,19 +8132,19 @@
         <v>50</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F50" s="36" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="G50" s="32" t="s">
         <v>2</v>
@@ -7708,7 +8178,7 @@
         <v>Kml.Modelo.3D</v>
       </c>
       <c r="P50" s="37" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="Q50" s="14" t="str">
         <f t="shared" si="10"/>
@@ -7718,7 +8188,7 @@
         <f t="shared" si="15"/>
         <v>Geographic feature element in KML. It allows you to insert complex 3D models (usually in COLLADA .dae format) into the map.</v>
       </c>
-      <c r="S50" s="14" t="s">
+      <c r="S50" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T50" s="14" t="str">
@@ -7734,7 +8204,7 @@
         <v>Kml.Modelo.3D</v>
       </c>
       <c r="W50" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X50" s="30" t="str">
         <f t="shared" si="19"/>
@@ -7756,7 +8226,7 @@
         <v>2</v>
       </c>
       <c r="AD50" s="37" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
     </row>
     <row r="51" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7764,19 +8234,19 @@
         <v>51</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F51" s="36" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="G51" s="32" t="s">
         <v>2</v>
@@ -7810,7 +8280,7 @@
         <v>Kml.Nome</v>
       </c>
       <c r="P51" s="37" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="Q51" s="14" t="str">
         <f t="shared" si="10"/>
@@ -7820,7 +8290,7 @@
         <f t="shared" si="15"/>
         <v>KML element. Defines a name that can be file, place, etc. &lt;name&gt;Element Name&lt;/name&gt;</v>
       </c>
-      <c r="S51" s="14" t="s">
+      <c r="S51" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T51" s="14" t="str">
@@ -7836,7 +8306,7 @@
         <v>Kml.Nome</v>
       </c>
       <c r="W51" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X51" s="30" t="str">
         <f t="shared" si="19"/>
@@ -7858,7 +8328,7 @@
         <v>2</v>
       </c>
       <c r="AD51" s="37" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
     </row>
     <row r="52" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7866,19 +8336,19 @@
         <v>52</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F52" s="36" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="G52" s="32" t="s">
         <v>2</v>
@@ -7912,7 +8382,7 @@
         <v>Kml.Pasta</v>
       </c>
       <c r="P52" s="37" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="Q52" s="14" t="str">
         <f t="shared" si="10"/>
@@ -7922,7 +8392,7 @@
         <f t="shared" si="15"/>
         <v>KML folder grouper element that sorts elements in folder hierarchy (such as the Google Earth sidebar), allows you to enable or disable block visibility.</v>
       </c>
-      <c r="S52" s="14" t="s">
+      <c r="S52" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T52" s="14" t="str">
@@ -7938,7 +8408,7 @@
         <v>Kml.Pasta</v>
       </c>
       <c r="W52" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X52" s="30" t="str">
         <f t="shared" si="19"/>
@@ -7960,7 +8430,7 @@
         <v>2</v>
       </c>
       <c r="AD52" s="37" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7968,19 +8438,19 @@
         <v>53</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F53" s="36" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="G53" s="32" t="s">
         <v>2</v>
@@ -8014,7 +8484,7 @@
         <v>Kml.Pasta.Aberta</v>
       </c>
       <c r="P53" s="37" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="Q53" s="14" t="str">
         <f t="shared" si="10"/>
@@ -8024,7 +8494,7 @@
         <f t="shared" si="15"/>
         <v>Specifies whether an item in the place tree in Google Earth or Google Maps is displayed open or closed by default &lt;open&gt;1&lt;/open&gt;</v>
       </c>
-      <c r="S53" s="14" t="s">
+      <c r="S53" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T53" s="14" t="str">
@@ -8040,7 +8510,7 @@
         <v>Kml.Pasta.Aberta</v>
       </c>
       <c r="W53" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X53" s="30" t="str">
         <f t="shared" si="19"/>
@@ -8062,7 +8532,7 @@
         <v>2</v>
       </c>
       <c r="AD53" s="37" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
     </row>
     <row r="54" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8070,19 +8540,19 @@
         <v>54</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F54" s="36" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="G54" s="32" t="s">
         <v>2</v>
@@ -8116,7 +8586,7 @@
         <v>Kml.Region</v>
       </c>
       <c r="P54" s="37" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="Q54" s="14" t="str">
         <f t="shared" si="10"/>
@@ -8126,7 +8596,7 @@
         <f t="shared" si="15"/>
         <v>KML element. Defines a region. &lt;Region&gt; ..... &lt;/Region&gt;</v>
       </c>
-      <c r="S54" s="14" t="s">
+      <c r="S54" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T54" s="14" t="str">
@@ -8142,7 +8612,7 @@
         <v>Kml.Region</v>
       </c>
       <c r="W54" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X54" s="30" t="str">
         <f t="shared" si="19"/>
@@ -8164,7 +8634,7 @@
         <v>2</v>
       </c>
       <c r="AD54" s="37" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
     </row>
     <row r="55" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8172,19 +8642,19 @@
         <v>55</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F55" s="36" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="G55" s="32" t="s">
         <v>2</v>
@@ -8218,7 +8688,7 @@
         <v>Kml.Sobrepor</v>
       </c>
       <c r="P55" s="37" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="Q55" s="14" t="str">
         <f t="shared" si="10"/>
@@ -8228,7 +8698,7 @@
         <f t="shared" si="15"/>
         <v>Overlay element in KML. Displays a fixed image on the app screen (such as logos, legends, or compasses) independent of the map navigation.</v>
       </c>
-      <c r="S55" s="14" t="s">
+      <c r="S55" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T55" s="14" t="str">
@@ -8244,7 +8714,7 @@
         <v>Kml.Sobrepor</v>
       </c>
       <c r="W55" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X55" s="30" t="str">
         <f t="shared" si="19"/>
@@ -8266,7 +8736,7 @@
         <v>2</v>
       </c>
       <c r="AD55" s="37" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
     </row>
     <row r="56" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8274,19 +8744,19 @@
         <v>56</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F56" s="36" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="G56" s="32" t="s">
         <v>2</v>
@@ -8320,7 +8790,7 @@
         <v>Kml.Sobrepor.Foto</v>
       </c>
       <c r="P56" s="37" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="Q56" s="14" t="str">
         <f t="shared" si="10"/>
@@ -8330,7 +8800,7 @@
         <f t="shared" si="15"/>
         <v>Overlay element in KML. Associates a photo with a specific geographic location, allowing gigapixel navigation or panoramic view.</v>
       </c>
-      <c r="S56" s="14" t="s">
+      <c r="S56" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T56" s="14" t="str">
@@ -8346,7 +8816,7 @@
         <v>Kml.Sobrepor.Foto</v>
       </c>
       <c r="W56" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X56" s="30" t="str">
         <f t="shared" si="19"/>
@@ -8368,7 +8838,7 @@
         <v>2</v>
       </c>
       <c r="AD56" s="37" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="57" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8376,19 +8846,19 @@
         <v>57</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F57" s="36" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="G57" s="32" t="s">
         <v>2</v>
@@ -8422,7 +8892,7 @@
         <v>Kml.Sobrepor.Piso</v>
       </c>
       <c r="P57" s="37" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="Q57" s="14" t="str">
         <f t="shared" si="10"/>
@@ -8432,7 +8902,7 @@
         <f t="shared" si="15"/>
         <v>Overlay element in KML. It projects a two-dimensional image directly onto the Earth's surface, aligned by geographic boundary coordinates.</v>
       </c>
-      <c r="S57" s="14" t="s">
+      <c r="S57" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T57" s="14" t="str">
@@ -8448,7 +8918,7 @@
         <v>Kml.Sobrepor.Piso</v>
       </c>
       <c r="W57" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X57" s="30" t="str">
         <f t="shared" si="19"/>
@@ -8470,7 +8940,7 @@
         <v>2</v>
       </c>
       <c r="AD57" s="37" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="58" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8478,19 +8948,19 @@
         <v>58</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F58" s="36" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="G58" s="32" t="s">
         <v>2</v>
@@ -8524,7 +8994,7 @@
         <v>Kml.Tempo.Intervalo</v>
       </c>
       <c r="P58" s="37" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="Q58" s="14" t="str">
         <f t="shared" si="10"/>
@@ -8534,7 +9004,7 @@
         <f t="shared" si="15"/>
         <v>Animation element in KML. Sets a time range with start (&lt;begin&gt;) and end () date/time&lt;end&gt;.</v>
       </c>
-      <c r="S58" s="14" t="s">
+      <c r="S58" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T58" s="14" t="str">
@@ -8550,7 +9020,7 @@
         <v>Kml.Tempo.Intervalo</v>
       </c>
       <c r="W58" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X58" s="30" t="str">
         <f t="shared" si="19"/>
@@ -8572,7 +9042,7 @@
         <v>2</v>
       </c>
       <c r="AD58" s="37" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="59" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8580,19 +9050,19 @@
         <v>59</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F59" s="36" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="G59" s="32" t="s">
         <v>2</v>
@@ -8626,7 +9096,7 @@
         <v>Kml.Tempo.Momento</v>
       </c>
       <c r="P59" s="37" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="Q59" s="14" t="str">
         <f t="shared" si="10"/>
@@ -8636,7 +9106,7 @@
         <f t="shared" si="15"/>
         <v>KML element. Defines a moment that can be a year, date, or time. &lt;when&gt;2024-08-01&lt;/when&gt;</v>
       </c>
-      <c r="S59" s="14" t="s">
+      <c r="S59" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T59" s="14" t="str">
@@ -8652,7 +9122,7 @@
         <v>Kml.Tempo.Momento</v>
       </c>
       <c r="W59" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X59" s="30" t="str">
         <f t="shared" si="19"/>
@@ -8674,7 +9144,7 @@
         <v>2</v>
       </c>
       <c r="AD59" s="37" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
     </row>
     <row r="60" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8682,19 +9152,19 @@
         <v>60</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F60" s="36" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="G60" s="32" t="s">
         <v>2</v>
@@ -8728,7 +9198,7 @@
         <v>Kml.Tempo.Momento.Final</v>
       </c>
       <c r="P60" s="37" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="Q60" s="14" t="str">
         <f t="shared" si="10"/>
@@ -8738,7 +9208,7 @@
         <f t="shared" si="15"/>
         <v>KML element. Sets an end moment in a &lt;TimeSpan&gt;. &lt;end&gt;2024-08-01&lt;/end&gt;</v>
       </c>
-      <c r="S60" s="14" t="s">
+      <c r="S60" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T60" s="14" t="str">
@@ -8754,7 +9224,7 @@
         <v>Kml.Tempo.Momento.Final</v>
       </c>
       <c r="W60" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X60" s="30" t="str">
         <f t="shared" si="19"/>
@@ -8776,7 +9246,7 @@
         <v>2</v>
       </c>
       <c r="AD60" s="37" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
     </row>
     <row r="61" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8784,19 +9254,19 @@
         <v>61</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F61" s="36" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="G61" s="32" t="s">
         <v>2</v>
@@ -8830,7 +9300,7 @@
         <v>Kml.Tempo.Momento.Inicial</v>
       </c>
       <c r="P61" s="37" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="Q61" s="14" t="str">
         <f t="shared" si="10"/>
@@ -8840,7 +9310,7 @@
         <f t="shared" si="15"/>
         <v>KML element. Sets a starting moment in a &lt;TimeSpan&gt;. &lt;begin&gt;2024-01-01&lt;/begin&gt;</v>
       </c>
-      <c r="S61" s="14" t="s">
+      <c r="S61" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T61" s="14" t="str">
@@ -8856,7 +9326,7 @@
         <v>Kml.Tempo.Momento.Inicial</v>
       </c>
       <c r="W61" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X61" s="30" t="str">
         <f t="shared" si="19"/>
@@ -8878,7 +9348,7 @@
         <v>2</v>
       </c>
       <c r="AD61" s="37" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
     </row>
     <row r="62" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8886,19 +9356,19 @@
         <v>62</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F62" s="36" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="G62" s="32" t="s">
         <v>2</v>
@@ -8932,7 +9402,7 @@
         <v>Kml.Tempo.Registra</v>
       </c>
       <c r="P62" s="37" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="Q62" s="14" t="str">
         <f t="shared" si="10"/>
@@ -8942,7 +9412,7 @@
         <f t="shared" si="15"/>
         <v>Animation element in KML. Associates an element with a specific point in time (e.g., point event).</v>
       </c>
-      <c r="S62" s="14" t="s">
+      <c r="S62" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T62" s="14" t="str">
@@ -8958,7 +9428,7 @@
         <v>Kml.Tempo.Registra</v>
       </c>
       <c r="W62" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X62" s="30" t="str">
         <f t="shared" si="19"/>
@@ -8980,27 +9450,27 @@
         <v>2</v>
       </c>
       <c r="AD62" s="37" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="63" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="63" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="31">
         <v>63</v>
       </c>
-      <c r="B63" s="63" t="s">
-        <v>331</v>
-      </c>
-      <c r="C63" s="64" t="s">
-        <v>332</v>
-      </c>
-      <c r="D63" s="64" t="s">
-        <v>334</v>
-      </c>
-      <c r="E63" s="64" t="s">
-        <v>333</v>
-      </c>
-      <c r="F63" s="64" t="s">
-        <v>335</v>
+      <c r="B63" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="C63" s="62" t="s">
+        <v>344</v>
+      </c>
+      <c r="D63" s="62" t="s">
+        <v>345</v>
+      </c>
+      <c r="E63" s="62" t="s">
+        <v>346</v>
+      </c>
+      <c r="F63" s="62" t="s">
+        <v>323</v>
       </c>
       <c r="G63" s="32" t="s">
         <v>2</v>
@@ -9018,50 +9488,50 @@
         <v>2</v>
       </c>
       <c r="L63" s="13" t="str">
-        <f t="shared" ref="L63:O67" si="20">SUBSTITUTE(CONCATENATE("", C63), ".", " ")</f>
-        <v>De API</v>
+        <f t="shared" si="11"/>
+        <v>API.Plataforma</v>
       </c>
       <c r="M63" s="13" t="str">
-        <f t="shared" si="20"/>
-        <v>Macros</v>
+        <f t="shared" si="11"/>
+        <v>API.Macros</v>
       </c>
       <c r="N63" s="13" t="str">
-        <f t="shared" si="20"/>
-        <v>Métodos</v>
+        <f t="shared" ref="N63:O67" si="20">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E63),"."," ")," De "," de "))</f>
+        <v>API Método</v>
       </c>
       <c r="O63" s="13" t="str">
         <f t="shared" si="20"/>
         <v>Função Auxiliar</v>
       </c>
       <c r="P63" s="14" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="Q63" s="14" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="R63" s="14" t="s">
-        <v>338</v>
-      </c>
-      <c r="S63" s="14" t="s">
+        <v>326</v>
+      </c>
+      <c r="S63" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T63" s="14" t="str">
         <f t="shared" ref="T63:V67" si="21">SUBSTITUTE(C63, ".", " ")</f>
-        <v>De API</v>
+        <v>API Plataforma</v>
       </c>
       <c r="U63" s="14" t="str">
         <f t="shared" si="21"/>
-        <v>Macros</v>
+        <v>API Macros</v>
       </c>
       <c r="V63" s="60" t="str">
         <f t="shared" si="21"/>
-        <v>Métodos</v>
+        <v>API Método</v>
       </c>
       <c r="W63" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X63" s="30" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="X63:X67" si="22">CONCATENATE("Key-Kml-",A63)</f>
         <v>Key-Kml-63</v>
       </c>
       <c r="Y63" s="61" t="s">
@@ -9083,24 +9553,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="31">
         <v>64</v>
       </c>
-      <c r="B64" s="63" t="s">
-        <v>331</v>
-      </c>
-      <c r="C64" s="64" t="s">
-        <v>332</v>
-      </c>
-      <c r="D64" s="64" t="s">
-        <v>334</v>
-      </c>
-      <c r="E64" s="64" t="s">
-        <v>333</v>
-      </c>
-      <c r="F64" s="64" t="s">
-        <v>339</v>
+      <c r="B64" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="C64" s="62" t="s">
+        <v>344</v>
+      </c>
+      <c r="D64" s="62" t="s">
+        <v>345</v>
+      </c>
+      <c r="E64" s="62" t="s">
+        <v>346</v>
+      </c>
+      <c r="F64" s="62" t="s">
+        <v>327</v>
       </c>
       <c r="G64" s="32" t="s">
         <v>2</v>
@@ -9118,50 +9588,50 @@
         <v>2</v>
       </c>
       <c r="L64" s="13" t="str">
-        <f t="shared" si="20"/>
-        <v>De API</v>
+        <f t="shared" ref="L64:M67" si="23">CONCATENATE("", C64)</f>
+        <v>API.Plataforma</v>
       </c>
       <c r="M64" s="13" t="str">
-        <f t="shared" si="20"/>
-        <v>Macros</v>
+        <f t="shared" si="23"/>
+        <v>API.Macros</v>
       </c>
       <c r="N64" s="13" t="str">
         <f t="shared" si="20"/>
-        <v>Métodos</v>
+        <v>API Método</v>
       </c>
       <c r="O64" s="13" t="str">
         <f t="shared" si="20"/>
         <v>Função Global</v>
       </c>
       <c r="P64" s="14" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="Q64" s="14" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="R64" s="14" t="s">
-        <v>342</v>
-      </c>
-      <c r="S64" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="S64" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T64" s="14" t="str">
         <f t="shared" si="21"/>
-        <v>De API</v>
+        <v>API Plataforma</v>
       </c>
       <c r="U64" s="14" t="str">
         <f t="shared" si="21"/>
-        <v>Macros</v>
+        <v>API Macros</v>
       </c>
       <c r="V64" s="60" t="str">
         <f t="shared" si="21"/>
-        <v>Métodos</v>
+        <v>API Método</v>
       </c>
       <c r="W64" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X64" s="30" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>Key-Kml-64</v>
       </c>
       <c r="Y64" s="61" t="s">
@@ -9183,25 +9653,25 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="31">
         <v>65</v>
       </c>
-      <c r="B65" s="63" t="s">
+      <c r="B65" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="C65" s="62" t="s">
+        <v>344</v>
+      </c>
+      <c r="D65" s="62" t="s">
+        <v>345</v>
+      </c>
+      <c r="E65" s="62" t="s">
+        <v>346</v>
+      </c>
+      <c r="F65" s="62" t="s">
         <v>331</v>
       </c>
-      <c r="C65" s="64" t="s">
-        <v>332</v>
-      </c>
-      <c r="D65" s="64" t="s">
-        <v>334</v>
-      </c>
-      <c r="E65" s="64" t="s">
-        <v>333</v>
-      </c>
-      <c r="F65" s="64" t="s">
-        <v>343</v>
-      </c>
       <c r="G65" s="32" t="s">
         <v>2</v>
       </c>
@@ -9218,50 +9688,50 @@
         <v>2</v>
       </c>
       <c r="L65" s="13" t="str">
-        <f t="shared" si="20"/>
-        <v>De API</v>
+        <f t="shared" si="23"/>
+        <v>API.Plataforma</v>
       </c>
       <c r="M65" s="13" t="str">
-        <f t="shared" si="20"/>
-        <v>Macros</v>
+        <f t="shared" si="23"/>
+        <v>API.Macros</v>
       </c>
       <c r="N65" s="13" t="str">
         <f t="shared" si="20"/>
-        <v>Métodos</v>
+        <v>API Método</v>
       </c>
       <c r="O65" s="13" t="str">
         <f t="shared" si="20"/>
         <v>Função Local</v>
       </c>
       <c r="P65" s="14" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="Q65" s="14" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="R65" s="14" t="s">
-        <v>346</v>
-      </c>
-      <c r="S65" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="S65" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T65" s="14" t="str">
         <f t="shared" si="21"/>
-        <v>De API</v>
+        <v>API Plataforma</v>
       </c>
       <c r="U65" s="14" t="str">
         <f t="shared" si="21"/>
-        <v>Macros</v>
+        <v>API Macros</v>
       </c>
       <c r="V65" s="60" t="str">
         <f t="shared" si="21"/>
-        <v>Métodos</v>
+        <v>API Método</v>
       </c>
       <c r="W65" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X65" s="30" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>Key-Kml-65</v>
       </c>
       <c r="Y65" s="61" t="s">
@@ -9283,24 +9753,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="31">
         <v>66</v>
       </c>
-      <c r="B66" s="63" t="s">
-        <v>331</v>
-      </c>
-      <c r="C66" s="64" t="s">
-        <v>332</v>
-      </c>
-      <c r="D66" s="64" t="s">
-        <v>334</v>
-      </c>
-      <c r="E66" s="64" t="s">
-        <v>333</v>
-      </c>
-      <c r="F66" s="64" t="s">
-        <v>347</v>
+      <c r="B66" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="C66" s="62" t="s">
+        <v>344</v>
+      </c>
+      <c r="D66" s="62" t="s">
+        <v>345</v>
+      </c>
+      <c r="E66" s="62" t="s">
+        <v>346</v>
+      </c>
+      <c r="F66" s="62" t="s">
+        <v>335</v>
       </c>
       <c r="G66" s="32" t="s">
         <v>2</v>
@@ -9318,50 +9788,50 @@
         <v>2</v>
       </c>
       <c r="L66" s="13" t="str">
-        <f t="shared" si="20"/>
-        <v>De API</v>
+        <f t="shared" si="23"/>
+        <v>API.Plataforma</v>
       </c>
       <c r="M66" s="13" t="str">
-        <f t="shared" si="20"/>
-        <v>Macros</v>
+        <f t="shared" si="23"/>
+        <v>API.Macros</v>
       </c>
       <c r="N66" s="13" t="str">
         <f t="shared" si="20"/>
-        <v>Métodos</v>
+        <v>API Método</v>
       </c>
       <c r="O66" s="13" t="str">
         <f t="shared" si="20"/>
         <v>Função Filtro</v>
       </c>
       <c r="P66" s="14" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="Q66" s="14" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="R66" s="14" t="s">
-        <v>350</v>
-      </c>
-      <c r="S66" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="S66" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T66" s="14" t="str">
         <f t="shared" si="21"/>
-        <v>De API</v>
+        <v>API Plataforma</v>
       </c>
       <c r="U66" s="14" t="str">
         <f t="shared" si="21"/>
-        <v>Macros</v>
+        <v>API Macros</v>
       </c>
       <c r="V66" s="60" t="str">
         <f t="shared" si="21"/>
-        <v>Métodos</v>
+        <v>API Método</v>
       </c>
       <c r="W66" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X66" s="30" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>Key-Kml-66</v>
       </c>
       <c r="Y66" s="61" t="s">
@@ -9383,24 +9853,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="31">
         <v>67</v>
       </c>
-      <c r="B67" s="63" t="s">
-        <v>331</v>
-      </c>
-      <c r="C67" s="64" t="s">
-        <v>332</v>
-      </c>
-      <c r="D67" s="64" t="s">
-        <v>334</v>
-      </c>
-      <c r="E67" s="64" t="s">
-        <v>351</v>
-      </c>
-      <c r="F67" s="64" t="s">
-        <v>352</v>
+      <c r="B67" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="C67" s="62" t="s">
+        <v>344</v>
+      </c>
+      <c r="D67" s="62" t="s">
+        <v>347</v>
+      </c>
+      <c r="E67" s="62" t="s">
+        <v>348</v>
+      </c>
+      <c r="F67" s="62" t="s">
+        <v>339</v>
       </c>
       <c r="G67" s="32" t="s">
         <v>2</v>
@@ -9418,50 +9888,50 @@
         <v>2</v>
       </c>
       <c r="L67" s="13" t="str">
-        <f t="shared" si="20"/>
-        <v>De API</v>
+        <f t="shared" si="23"/>
+        <v>API.Plataforma</v>
       </c>
       <c r="M67" s="13" t="str">
-        <f t="shared" si="20"/>
-        <v>Macros</v>
+        <f t="shared" si="23"/>
+        <v>API.Macros.Visuais</v>
       </c>
       <c r="N67" s="13" t="str">
         <f t="shared" si="20"/>
-        <v>Códigos Visuais</v>
+        <v>API Método Visual</v>
       </c>
       <c r="O67" s="13" t="str">
         <f t="shared" si="20"/>
         <v>Bloco de Código</v>
       </c>
       <c r="P67" s="14" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="Q67" s="14" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="R67" s="14" t="s">
-        <v>355</v>
-      </c>
-      <c r="S67" s="14" t="s">
+        <v>342</v>
+      </c>
+      <c r="S67" s="63" t="s">
         <v>2</v>
       </c>
       <c r="T67" s="14" t="str">
         <f t="shared" si="21"/>
-        <v>De API</v>
+        <v>API Plataforma</v>
       </c>
       <c r="U67" s="14" t="str">
         <f t="shared" si="21"/>
-        <v>Macros</v>
+        <v>API Macros Visuais</v>
       </c>
       <c r="V67" s="60" t="str">
         <f t="shared" si="21"/>
-        <v>Códigos Visuais</v>
+        <v>API Método Visual</v>
       </c>
       <c r="W67" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X67" s="30" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>Key-Kml-67</v>
       </c>
       <c r="Y67" s="61" t="s">
@@ -9487,27 +9957,25 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD62">
     <sortCondition ref="F30:F62"/>
   </sortState>
-  <conditionalFormatting sqref="A2:B67">
-    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
+  <conditionalFormatting sqref="A2:B62 A63:A67">
+    <cfRule type="cellIs" dxfId="32" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E67:F67">
-    <cfRule type="duplicateValues" dxfId="31" priority="2"/>
+  <conditionalFormatting sqref="F1:F62">
+    <cfRule type="duplicateValues" dxfId="31" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F62">
-    <cfRule type="duplicateValues" dxfId="30" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F63:F66">
-    <cfRule type="duplicateValues" dxfId="29" priority="3"/>
+  <conditionalFormatting sqref="F63:F67">
+    <cfRule type="duplicateValues" dxfId="30" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="28" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="14" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC1:AD1">
-    <cfRule type="cellIs" dxfId="27" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9529,67 +9997,67 @@
   <sheetData>
     <row r="1" spans="1:21" s="18" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="I1" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="J1" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="K1" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="L1" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="M1" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="N1" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="O1" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="P1" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="Q1" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="R1" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="S1" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="T1" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="U1" s="17" t="s">
         <v>79</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="P1" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q1" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="R1" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="S1" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="T1" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="U1" s="17" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.15">
@@ -9687,22 +10155,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C1" s="26" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D1" s="26" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E1" s="26" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="F1" s="26" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="G1" s="26" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9855,10 +10323,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="39" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="C2" s="56" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="D2" s="46" t="s">
         <v>2</v>
@@ -9891,10 +10359,10 @@
         <v>2</v>
       </c>
       <c r="N2" s="47" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="O2" s="57" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="P2" s="49" t="s">
         <v>2</v>
@@ -9926,16 +10394,16 @@
         <v>3</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="C3" s="56" t="s">
+        <v>314</v>
+      </c>
+      <c r="D3" s="46" t="s">
         <v>322</v>
       </c>
-      <c r="D3" s="46" t="s">
-        <v>330</v>
-      </c>
       <c r="E3" s="39" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="F3" s="46" t="s">
         <v>2</v>
@@ -9962,10 +10430,10 @@
         <v>2</v>
       </c>
       <c r="N3" s="47" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="O3" s="57" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="P3" s="49" t="s">
         <v>2</v>
@@ -9997,16 +10465,16 @@
         <v>4</v>
       </c>
       <c r="B4" s="39" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="C4" s="56" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="D4" s="46" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="E4" s="39" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="F4" s="46" t="s">
         <v>2</v>
@@ -10033,10 +10501,10 @@
         <v>2</v>
       </c>
       <c r="N4" s="47" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="O4" s="57" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="P4" s="49" t="s">
         <v>2</v>
@@ -10068,16 +10536,16 @@
         <v>5</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="C5" s="56" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="D5" s="46" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="E5" s="39" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="F5" s="46" t="s">
         <v>2</v>
@@ -10104,10 +10572,10 @@
         <v>2</v>
       </c>
       <c r="N5" s="47" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="O5" s="57" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="P5" s="49" t="s">
         <v>2</v>
@@ -10139,16 +10607,16 @@
         <v>6</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C6" s="56" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="E6" s="39" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="F6" s="46" t="s">
         <v>2</v>
@@ -10175,10 +10643,10 @@
         <v>2</v>
       </c>
       <c r="N6" s="47" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="O6" s="57" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="P6" s="49" t="s">
         <v>2</v>
@@ -10210,10 +10678,10 @@
         <v>7</v>
       </c>
       <c r="B7" s="39" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C7" s="56" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="D7" s="46" t="s">
         <v>2</v>
@@ -10246,10 +10714,10 @@
         <v>2</v>
       </c>
       <c r="N7" s="47" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="O7" s="57" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="P7" s="49" t="s">
         <v>2</v>
@@ -10281,16 +10749,16 @@
         <v>8</v>
       </c>
       <c r="B8" s="39" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="C8" s="56" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D8" s="51" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="E8" s="39" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="F8" s="46" t="s">
         <v>2</v>
@@ -10317,10 +10785,10 @@
         <v>2</v>
       </c>
       <c r="N8" s="47" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="O8" s="48" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="P8" s="49" t="s">
         <v>2</v>
@@ -10352,22 +10820,22 @@
         <v>9</v>
       </c>
       <c r="B9" s="39" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="C9" s="56" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="D9" s="51" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="E9" s="39" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="F9" s="46" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="H9" s="46" t="s">
         <v>2</v>
@@ -10388,10 +10856,10 @@
         <v>2</v>
       </c>
       <c r="N9" s="47" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="O9" s="48" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="P9" s="49" t="s">
         <v>2</v>
@@ -10423,22 +10891,22 @@
         <v>10</v>
       </c>
       <c r="B10" s="39" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C10" s="56" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="D10" s="51" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="E10" s="39" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="F10" s="46" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="H10" s="46" t="s">
         <v>2</v>
@@ -10459,10 +10927,10 @@
         <v>2</v>
       </c>
       <c r="N10" s="47" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="O10" s="48" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="P10" s="49" t="s">
         <v>2</v>
@@ -10494,22 +10962,22 @@
         <v>11</v>
       </c>
       <c r="B11" s="39" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C11" s="56" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="D11" s="51" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="E11" s="39" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="F11" s="46" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="H11" s="46" t="s">
         <v>2</v>
@@ -10530,10 +10998,10 @@
         <v>2</v>
       </c>
       <c r="N11" s="47" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="O11" s="48" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="P11" s="49" t="s">
         <v>2</v>
@@ -10565,22 +11033,22 @@
         <v>12</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="C12" s="56" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="D12" s="51" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="E12" s="39" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="F12" s="46" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="H12" s="46" t="s">
         <v>2</v>
@@ -10589,28 +11057,28 @@
         <v>2</v>
       </c>
       <c r="J12" s="51" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="K12" s="39" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="L12" s="51" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="M12" s="39" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="N12" s="47" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="O12" s="48" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="P12" s="47" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="Q12" s="50" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="R12" s="49" t="s">
         <v>2</v>
@@ -10636,22 +11104,22 @@
         <v>13</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="C13" s="56" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="D13" s="51" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="E13" s="39" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="F13" s="46" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="H13" s="46" t="s">
         <v>2</v>
@@ -10660,28 +11128,28 @@
         <v>2</v>
       </c>
       <c r="J13" s="51" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="K13" s="39" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="L13" s="51" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="M13" s="39" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="N13" s="47" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="O13" s="48" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="P13" s="47" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="Q13" s="50" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="R13" s="49" t="s">
         <v>2</v>
@@ -10707,22 +11175,22 @@
         <v>14</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="C14" s="56" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="D14" s="51" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="E14" s="39" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="F14" s="46" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="H14" s="46" t="s">
         <v>2</v>
@@ -10731,28 +11199,28 @@
         <v>2</v>
       </c>
       <c r="J14" s="51" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="K14" s="39" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="L14" s="51" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="M14" s="39" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="N14" s="47" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="O14" s="48" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="P14" s="47" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="Q14" s="50" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="R14" s="49" t="s">
         <v>2</v>
@@ -10778,52 +11246,52 @@
         <v>15</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="C15" s="56" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="D15" s="51" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="E15" s="39" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="F15" s="46" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="G15" s="39" t="s">
+        <v>292</v>
+      </c>
+      <c r="H15" s="46" t="s">
+        <v>2</v>
+      </c>
+      <c r="I15" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="J15" s="51" t="s">
+        <v>277</v>
+      </c>
+      <c r="K15" s="39" t="s">
+        <v>294</v>
+      </c>
+      <c r="L15" s="51" t="s">
+        <v>277</v>
+      </c>
+      <c r="M15" s="39" t="s">
+        <v>295</v>
+      </c>
+      <c r="N15" s="47" t="s">
+        <v>310</v>
+      </c>
+      <c r="O15" s="48" t="s">
         <v>300</v>
       </c>
-      <c r="H15" s="46" t="s">
-        <v>2</v>
-      </c>
-      <c r="I15" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="J15" s="51" t="s">
-        <v>285</v>
-      </c>
-      <c r="K15" s="39" t="s">
-        <v>302</v>
-      </c>
-      <c r="L15" s="51" t="s">
-        <v>285</v>
-      </c>
-      <c r="M15" s="39" t="s">
-        <v>303</v>
-      </c>
-      <c r="N15" s="47" t="s">
-        <v>318</v>
-      </c>
-      <c r="O15" s="48" t="s">
-        <v>308</v>
-      </c>
       <c r="P15" s="47" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="Q15" s="50" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="R15" s="49" t="s">
         <v>2</v>
@@ -10849,23 +11317,23 @@
         <v>16</v>
       </c>
       <c r="B16" s="39" t="s">
+        <v>284</v>
+      </c>
+      <c r="C16" s="56" t="s">
+        <v>149</v>
+      </c>
+      <c r="D16" s="51" t="s">
+        <v>277</v>
+      </c>
+      <c r="E16" s="39" t="s">
+        <v>275</v>
+      </c>
+      <c r="F16" s="46" t="s">
+        <v>322</v>
+      </c>
+      <c r="G16" s="39" t="s">
         <v>292</v>
       </c>
-      <c r="C16" s="56" t="s">
-        <v>157</v>
-      </c>
-      <c r="D16" s="51" t="s">
-        <v>285</v>
-      </c>
-      <c r="E16" s="39" t="s">
-        <v>283</v>
-      </c>
-      <c r="F16" s="46" t="s">
-        <v>330</v>
-      </c>
-      <c r="G16" s="39" t="s">
-        <v>300</v>
-      </c>
       <c r="H16" s="46" t="s">
         <v>2</v>
       </c>
@@ -10873,28 +11341,28 @@
         <v>2</v>
       </c>
       <c r="J16" s="51" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="K16" s="39" t="s">
+        <v>294</v>
+      </c>
+      <c r="L16" s="51" t="s">
+        <v>277</v>
+      </c>
+      <c r="M16" s="39" t="s">
+        <v>295</v>
+      </c>
+      <c r="N16" s="47" t="s">
+        <v>310</v>
+      </c>
+      <c r="O16" s="48" t="s">
         <v>302</v>
       </c>
-      <c r="L16" s="51" t="s">
-        <v>285</v>
-      </c>
-      <c r="M16" s="39" t="s">
-        <v>303</v>
-      </c>
-      <c r="N16" s="47" t="s">
-        <v>318</v>
-      </c>
-      <c r="O16" s="48" t="s">
-        <v>310</v>
-      </c>
       <c r="P16" s="47" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="Q16" s="50" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="R16" s="49" t="s">
         <v>2</v>
@@ -10920,22 +11388,22 @@
         <v>17</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="C17" s="56" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="D17" s="51" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="E17" s="39" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="F17" s="46" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="G17" s="39" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="H17" s="46" t="s">
         <v>2</v>
@@ -10944,28 +11412,28 @@
         <v>2</v>
       </c>
       <c r="J17" s="51" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="K17" s="39" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="L17" s="51" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="M17" s="39" t="s">
+        <v>295</v>
+      </c>
+      <c r="N17" s="47" t="s">
+        <v>310</v>
+      </c>
+      <c r="O17" s="48" t="s">
         <v>303</v>
       </c>
-      <c r="N17" s="47" t="s">
-        <v>318</v>
-      </c>
-      <c r="O17" s="48" t="s">
-        <v>311</v>
-      </c>
       <c r="P17" s="47" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="Q17" s="50" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="R17" s="49" t="s">
         <v>2</v>
@@ -10991,52 +11459,52 @@
         <v>18</v>
       </c>
       <c r="B18" s="39" t="s">
+        <v>286</v>
+      </c>
+      <c r="C18" s="56" t="s">
+        <v>149</v>
+      </c>
+      <c r="D18" s="51" t="s">
+        <v>277</v>
+      </c>
+      <c r="E18" s="39" t="s">
+        <v>275</v>
+      </c>
+      <c r="F18" s="46" t="s">
+        <v>322</v>
+      </c>
+      <c r="G18" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="H18" s="46" t="s">
+        <v>2</v>
+      </c>
+      <c r="I18" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="J18" s="51" t="s">
+        <v>277</v>
+      </c>
+      <c r="K18" s="39" t="s">
         <v>294</v>
       </c>
-      <c r="C18" s="56" t="s">
-        <v>157</v>
-      </c>
-      <c r="D18" s="51" t="s">
-        <v>285</v>
-      </c>
-      <c r="E18" s="39" t="s">
-        <v>283</v>
-      </c>
-      <c r="F18" s="46" t="s">
-        <v>330</v>
-      </c>
-      <c r="G18" s="39" t="s">
-        <v>301</v>
-      </c>
-      <c r="H18" s="46" t="s">
-        <v>2</v>
-      </c>
-      <c r="I18" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="J18" s="51" t="s">
-        <v>285</v>
-      </c>
-      <c r="K18" s="39" t="s">
-        <v>302</v>
-      </c>
       <c r="L18" s="51" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="M18" s="39" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="N18" s="47" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="O18" s="48" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="P18" s="47" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="Q18" s="50" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="R18" s="49" t="s">
         <v>2</v>
@@ -11062,52 +11530,52 @@
         <v>19</v>
       </c>
       <c r="B19" s="39" t="s">
+        <v>287</v>
+      </c>
+      <c r="C19" s="56" t="s">
+        <v>149</v>
+      </c>
+      <c r="D19" s="51" t="s">
+        <v>277</v>
+      </c>
+      <c r="E19" s="39" t="s">
+        <v>275</v>
+      </c>
+      <c r="F19" s="46" t="s">
+        <v>322</v>
+      </c>
+      <c r="G19" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="H19" s="46" t="s">
+        <v>2</v>
+      </c>
+      <c r="I19" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="J19" s="51" t="s">
+        <v>277</v>
+      </c>
+      <c r="K19" s="39" t="s">
+        <v>294</v>
+      </c>
+      <c r="L19" s="51" t="s">
+        <v>277</v>
+      </c>
+      <c r="M19" s="39" t="s">
         <v>295</v>
       </c>
-      <c r="C19" s="56" t="s">
-        <v>157</v>
-      </c>
-      <c r="D19" s="51" t="s">
-        <v>285</v>
-      </c>
-      <c r="E19" s="39" t="s">
-        <v>283</v>
-      </c>
-      <c r="F19" s="46" t="s">
-        <v>330</v>
-      </c>
-      <c r="G19" s="39" t="s">
-        <v>301</v>
-      </c>
-      <c r="H19" s="46" t="s">
-        <v>2</v>
-      </c>
-      <c r="I19" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="J19" s="51" t="s">
-        <v>285</v>
-      </c>
-      <c r="K19" s="39" t="s">
-        <v>302</v>
-      </c>
-      <c r="L19" s="51" t="s">
-        <v>285</v>
-      </c>
-      <c r="M19" s="39" t="s">
-        <v>303</v>
-      </c>
       <c r="N19" s="47" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="O19" s="48" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="P19" s="47" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="Q19" s="50" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="R19" s="49" t="s">
         <v>2</v>
@@ -11133,22 +11601,22 @@
         <v>20</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C20" s="56" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="D20" s="51" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="E20" s="39" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="F20" s="46" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="G20" s="39" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="H20" s="46" t="s">
         <v>2</v>
@@ -11157,28 +11625,28 @@
         <v>2</v>
       </c>
       <c r="J20" s="51" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="K20" s="39" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="L20" s="51" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="M20" s="39" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="N20" s="47" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="O20" s="48" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="P20" s="47" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="Q20" s="50" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="R20" s="49" t="s">
         <v>2</v>
@@ -11204,52 +11672,52 @@
         <v>21</v>
       </c>
       <c r="B21" s="39" t="s">
+        <v>289</v>
+      </c>
+      <c r="C21" s="56" t="s">
+        <v>149</v>
+      </c>
+      <c r="D21" s="51" t="s">
+        <v>277</v>
+      </c>
+      <c r="E21" s="39" t="s">
+        <v>275</v>
+      </c>
+      <c r="F21" s="46" t="s">
+        <v>322</v>
+      </c>
+      <c r="G21" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="H21" s="46" t="s">
+        <v>2</v>
+      </c>
+      <c r="I21" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="J21" s="51" t="s">
+        <v>277</v>
+      </c>
+      <c r="K21" s="39" t="s">
+        <v>294</v>
+      </c>
+      <c r="L21" s="51" t="s">
+        <v>277</v>
+      </c>
+      <c r="M21" s="39" t="s">
+        <v>295</v>
+      </c>
+      <c r="N21" s="47" t="s">
+        <v>310</v>
+      </c>
+      <c r="O21" s="48" t="s">
+        <v>307</v>
+      </c>
+      <c r="P21" s="47" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q21" s="50" t="s">
         <v>297</v>
-      </c>
-      <c r="C21" s="56" t="s">
-        <v>157</v>
-      </c>
-      <c r="D21" s="51" t="s">
-        <v>285</v>
-      </c>
-      <c r="E21" s="39" t="s">
-        <v>283</v>
-      </c>
-      <c r="F21" s="46" t="s">
-        <v>330</v>
-      </c>
-      <c r="G21" s="39" t="s">
-        <v>301</v>
-      </c>
-      <c r="H21" s="46" t="s">
-        <v>2</v>
-      </c>
-      <c r="I21" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="J21" s="51" t="s">
-        <v>285</v>
-      </c>
-      <c r="K21" s="39" t="s">
-        <v>302</v>
-      </c>
-      <c r="L21" s="51" t="s">
-        <v>285</v>
-      </c>
-      <c r="M21" s="39" t="s">
-        <v>303</v>
-      </c>
-      <c r="N21" s="47" t="s">
-        <v>318</v>
-      </c>
-      <c r="O21" s="48" t="s">
-        <v>315</v>
-      </c>
-      <c r="P21" s="47" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q21" s="50" t="s">
-        <v>305</v>
       </c>
       <c r="R21" s="49" t="s">
         <v>2</v>
@@ -11275,22 +11743,22 @@
         <v>22</v>
       </c>
       <c r="B22" s="39" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C22" s="56" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="D22" s="51" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="E22" s="39" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="F22" s="46" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="G22" s="39" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="H22" s="46" t="s">
         <v>2</v>
@@ -11299,28 +11767,28 @@
         <v>2</v>
       </c>
       <c r="J22" s="51" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="K22" s="39" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="L22" s="51" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="M22" s="39" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="N22" s="47" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="O22" s="48" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="P22" s="47" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="Q22" s="50" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="R22" s="49" t="s">
         <v>2</v>
@@ -11346,22 +11814,22 @@
         <v>23</v>
       </c>
       <c r="B23" s="39" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="C23" s="56" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="D23" s="51" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="E23" s="39" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="F23" s="46" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="G23" s="39" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="H23" s="46" t="s">
         <v>2</v>
@@ -11370,28 +11838,28 @@
         <v>2</v>
       </c>
       <c r="J23" s="51" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="K23" s="39" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="L23" s="51" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="M23" s="39" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="N23" s="47" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="O23" s="48" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="P23" s="47" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="Q23" s="50" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="R23" s="49" t="s">
         <v>2</v>
